--- a/04_DESIGN_TABLES/DesignTable_2404_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2404_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ58"/>
+  <dimension ref="A1:AQ60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5805,17 +5805,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2404-16-12</t>
+          <t>2404-14-12</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="C36" t="n">
-        <v>0.79386</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>1.375</v>
+        <v>1.25</v>
       </c>
       <c r="E36" t="n">
         <v>0.51241</v>
@@ -5845,16 +5845,16 @@
         <v>0.45527</v>
       </c>
       <c r="N36" t="n">
-        <v>0.65625</v>
+        <v>0.59375</v>
       </c>
       <c r="O36" t="n">
         <v>0.125</v>
       </c>
       <c r="P36" t="n">
-        <v>0.4365</v>
+        <v>0.4155</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.5965</v>
+        <v>0.534</v>
       </c>
       <c r="R36" t="n">
         <v>0.1292</v>
@@ -5869,13 +5869,13 @@
         <v>37</v>
       </c>
       <c r="V36" t="n">
-        <v>1.3125</v>
+        <v>1.1875</v>
       </c>
       <c r="W36" t="n">
         <v>0.08333</v>
       </c>
       <c r="X36" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.7305</v>
       </c>
       <c r="Y36" t="n">
         <v>0.04511</v>
@@ -5890,22 +5890,22 @@
         <v>0.719</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.17</v>
+        <v>0.975</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.844</v>
+        <v>0.719</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.115</v>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>2404-16-12</t>
+          <t>2404-14-12</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 1 5/16-12 x 3/4-14</t>
+          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 1 3/16-12 x 3/4-14</t>
         </is>
       </c>
       <c r="AH36" t="inlineStr">
@@ -5920,22 +5920,27 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>1 5/16-12</t>
+          <t>1 3/16-12</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>Brennan STEP measured == MS33656J published (VERIFIED) | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: through passage = the smaller of D / D1, the end carrying the larger counterbored to depth S (MS51500G Note 5 and its S column; hand-made 2404 table CBCUT columns)</t>
+          <t>OMi-only SKU (absent from Air-Way); dropped by the 2026-09-23 crawl (adapters77 2026-10-16); L / hex / bores: OMi WebsitePartsInfo2026 Items (= Brennan TFA p.6 on every cell; OMi and Brennan count as one source); JIC end MS33656J chain, NPTF end ASME + ENDL; bores: two published bores, step at the hex mid-plane | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex / bores: review table = OMi WebsitePartsInfo2026 (identical values, checked 2026-10-09; first appended from the Brennan product drawing 2026-09-05 - OMi-only size: absent from Air-Way and MS51500G; OMi's data are Brennan's, evidence 2026-09-26 -&gt; one source, ASSUMED); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: two bores - the review-table counterbore CBDIA on its end, D3 through the rest - stepped at the HEX MID-PLANE (user 2026-10-09, Q-2404-BORE: the hole is not the same throughout (from OMi); ASSUMPTION for the step: no depth is published for this size - Air-Way prints none, MS51500G does not list it - Air-Way's 2404 / 2404-L drawings show the step inside the hex (2404-L at its middle), and the 14 two-bore 2404 parts measured 2026-10-01 have it at the hex mid-plane within 0.0005 - ASSUMED)</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; L / hex / bores from OMi Items (= the Brennan TFA catalog p.6 on every cell, one source); end details from the end library</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>2404-16-12</t>
+          <t>2404-14-12</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
@@ -5947,19 +5952,16 @@
         <is>
           <t>Trivalent Cr3 Zinc</t>
         </is>
-      </c>
-      <c r="AQ36" t="n">
-        <v>3000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2404-16-16</t>
+          <t>2404-16-08</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="C37" t="n">
         <v>0.79386</v>
@@ -5968,31 +5970,31 @@
         <v>1.375</v>
       </c>
       <c r="E37" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.40779</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6828</v>
+        <v>0.5337</v>
       </c>
       <c r="G37" t="n">
         <v>1.7899</v>
       </c>
       <c r="H37" t="n">
-        <v>0.2572</v>
+        <v>0.2163</v>
       </c>
       <c r="I37" t="n">
-        <v>1.2832</v>
+        <v>0.81557</v>
       </c>
       <c r="J37" t="n">
-        <v>0.6828</v>
+        <v>0.5337</v>
       </c>
       <c r="K37" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.40779</v>
       </c>
       <c r="M37" t="n">
-        <v>0.57203</v>
+        <v>0.35064</v>
       </c>
       <c r="N37" t="n">
         <v>0.65625</v>
@@ -6037,25 +6039,25 @@
         <v>0.08333</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.531</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.13</v>
+        <v>0.9745</v>
       </c>
       <c r="AD37" t="n">
         <v>0.844</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.17</v>
+        <v>1.1355</v>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>2404-16-16</t>
+          <t>2404-16-08</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 1 5/16-12 x 1-11 1/2</t>
+          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 1 5/16-12 x 1/2-14</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
@@ -6065,7 +6067,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF</t>
+          <t>1/2-14 NPTF</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -6075,17 +6077,22 @@
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>Brennan STEP measured == MS33656J published (VERIFIED) | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: through passage = the smaller of D / D1, the end carrying the larger counterbored to depth S (MS51500G Note 5 and its S column; hand-made 2404 table CBCUT columns)</t>
+          <t>OMi-only SKU (absent from Air-Way); dropped by the 2026-09-23 crawl (adapters77 2026-10-16); L / hex / bores: OMi WebsitePartsInfo2026 Items (= Brennan TFA p.6 on every cell; OMi and Brennan count as one source); JIC end MS33656J chain, NPTF end ASME + ENDL; bores: two published bores, step at the hex mid-plane | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex / bores: review table = OMi WebsitePartsInfo2026 (identical values, checked 2026-10-09; first appended from the Brennan product drawing 2026-09-05 - OMi-only size: absent from Air-Way and MS51500G; OMi's data are Brennan's, evidence 2026-09-26 -&gt; one source, ASSUMED); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: two bores - the review-table counterbore CBDIA on its end, D3 through the rest - stepped at the HEX MID-PLANE (user 2026-10-09, Q-2404-BORE: the hole is not the same throughout (from OMi); ASSUMPTION for the step: no depth is published for this size - Air-Way prints none, MS51500G does not list it - Air-Way's 2404 / 2404-L drawings show the step inside the hex (2404-L at its middle), and the 14 two-bore 2404 parts measured 2026-10-01 have it at the hex mid-plane within 0.0005 - ASSUMED)</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; L / hex / bores from OMi Items (= the Brennan TFA catalog p.6 on every cell, one source); end details from the end library</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>2404-16-16</t>
+          <t>2404-16-08</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
@@ -6097,52 +6104,49 @@
         <is>
           <t>Trivalent Cr3 Zinc</t>
         </is>
-      </c>
-      <c r="AQ37" t="n">
-        <v>3000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2404-16-20</t>
+          <t>2404-16-12</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.4</v>
+        <v>2.11</v>
       </c>
       <c r="C38" t="n">
-        <v>0.97572</v>
+        <v>0.79386</v>
       </c>
       <c r="D38" t="n">
-        <v>1.69</v>
+        <v>1.375</v>
       </c>
       <c r="E38" t="n">
-        <v>0.81335</v>
+        <v>0.51241</v>
       </c>
       <c r="F38" t="n">
-        <v>0.7068</v>
+        <v>0.5457</v>
       </c>
       <c r="G38" t="n">
         <v>1.7899</v>
       </c>
       <c r="H38" t="n">
-        <v>0.2632</v>
+        <v>0.2043</v>
       </c>
       <c r="I38" t="n">
-        <v>1.6267</v>
+        <v>1.02482</v>
       </c>
       <c r="J38" t="n">
-        <v>0.7068</v>
+        <v>0.5457</v>
       </c>
       <c r="K38" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>0.81335</v>
+        <v>0.51241</v>
       </c>
       <c r="M38" t="n">
-        <v>0.74378</v>
+        <v>0.45527</v>
       </c>
       <c r="N38" t="n">
         <v>0.65625</v>
@@ -6187,25 +6191,25 @@
         <v>0.08333</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.25</v>
+        <v>0.719</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.2295</v>
+        <v>1.17</v>
       </c>
       <c r="AD38" t="n">
         <v>0.844</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.1705</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>2404-16-20</t>
+          <t>2404-16-12</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 1 5/16-12 x 1 1/4-11 1/2</t>
+          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 1 5/16-12 x 3/4-14</t>
         </is>
       </c>
       <c r="AH38" t="inlineStr">
@@ -6215,7 +6219,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPTF</t>
+          <t>3/4-14 NPTF</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -6225,22 +6229,17 @@
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>Brennan STEP measured == MS33656J published (VERIFIED) ; bores: OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 513 (= Air-Way D / D1 to rounding) (2026-10-09) | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: two bores - the review-table counterbore CBDIA on its end, D3 through the rest - stepped at the HEX MID-PLANE (user 2026-10-09, Q-2404-BORE: the hole is not the same throughout (from OMi); ASSUMPTION for the step: no depth is published for this size - Air-Way prints none, MS51500G does not list it - Air-Way's 2404 / 2404-L drawings show the step inside the hex (2404-L at its middle), and the 14 two-bore 2404 parts measured 2026-10-01 have it at the hex mid-plane within 0.0005 - ASSUMED)</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>2026-10-09 Q-2404-BORE (user, from OMi: the hole is not the same throughout): two bores, JIC 0.844 / pipe 1.25 from OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 513 (= Air-Way D / D1 to rounding); step at the hex mid-plane (Air-Way prints no depth, its drawing shows the step inside the hex)</t>
+          <t>Brennan STEP measured == MS33656J published (VERIFIED) | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: through passage = the smaller of D / D1, the end carrying the larger counterbored to depth S (MS51500G Note 5 and its S column; hand-made 2404 table CBCUT columns)</t>
         </is>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>2404-16-20</t>
+          <t>2404-16-12</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -6254,50 +6253,50 @@
         </is>
       </c>
       <c r="AQ38" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2404-16-24</t>
+          <t>2404-16-16</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2.51</v>
+        <v>2.3</v>
       </c>
       <c r="C39" t="n">
-        <v>1.1547</v>
+        <v>0.79386</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>1.375</v>
       </c>
       <c r="E39" t="n">
-        <v>0.93283</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="F39" t="n">
-        <v>0.7235</v>
+        <v>0.6828</v>
       </c>
       <c r="G39" t="n">
         <v>1.7899</v>
       </c>
       <c r="H39" t="n">
-        <v>0.2765</v>
+        <v>0.2572</v>
       </c>
       <c r="I39" t="n">
-        <v>1.86566</v>
+        <v>1.2832</v>
       </c>
       <c r="J39" t="n">
-        <v>0.7235</v>
+        <v>0.6828</v>
       </c>
       <c r="K39" t="n">
         <v>0.08696</v>
       </c>
       <c r="L39" t="n">
-        <v>0.93283</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="M39" t="n">
-        <v>0.86326</v>
+        <v>0.57203</v>
       </c>
       <c r="N39" t="n">
         <v>0.65625</v>
@@ -6342,25 +6341,25 @@
         <v>0.08333</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.5</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.2995</v>
+        <v>1.13</v>
       </c>
       <c r="AD39" t="n">
         <v>0.844</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.2105</v>
+        <v>1.17</v>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>2404-16-24</t>
+          <t>2404-16-16</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 1 5/16-12 x 1 1/2-11 1/2</t>
+          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 1 5/16-12 x 1-11 1/2</t>
         </is>
       </c>
       <c r="AH39" t="inlineStr">
@@ -6370,7 +6369,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>1 1/2-11 1/2 NPTF</t>
+          <t>1-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
@@ -6380,22 +6379,17 @@
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>Brennan STEP measured == MS33656J published (VERIFIED) ; bores: OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 514 (= Air-Way D / D1 to rounding) (2026-10-09) | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: two bores - the review-table counterbore CBDIA on its end, D3 through the rest - stepped at the HEX MID-PLANE (user 2026-10-09, Q-2404-BORE: the hole is not the same throughout (from OMi); ASSUMPTION for the step: no depth is published for this size - Air-Way prints none, MS51500G does not list it - Air-Way's 2404 / 2404-L drawings show the step inside the hex (2404-L at its middle), and the 14 two-bore 2404 parts measured 2026-10-01 have it at the hex mid-plane within 0.0005 - ASSUMED)</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>RESOLVED: L=2.51 - Air-Way+Brennan drawing agree on 2.51 (Parker 2.50 outvoted 2-1, 2026-09-05) ; 2026-10-09 Q-2404-BORE (user, from OMi: the hole is not the same throughout): two bores, JIC 0.844 / pipe 1.5 from OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 514 (= Air-Way D / D1 to rounding); step at the hex mid-plane (Air-Way prints no depth, its drawing shows the step inside the hex) | DataStatus VERIFIED -&gt; ASSUMED: counterbore depth unpublished: step at the hex mid-plane (Brennan-measured rule, single manufacturer)</t>
+          <t>Brennan STEP measured == MS33656J published (VERIFIED) | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: through passage = the smaller of D / D1, the end carrying the larger counterbored to depth S (MS51500G Note 5 and its S column; hand-made 2404 table CBCUT columns)</t>
         </is>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>2404-16-24</t>
+          <t>2404-16-16</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -6409,50 +6403,50 @@
         </is>
       </c>
       <c r="AQ39" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2404-16-32</t>
+          <t>2404-16-20</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.69</v>
+        <v>2.4</v>
       </c>
       <c r="C40" t="n">
-        <v>1.44338</v>
+        <v>0.97572</v>
       </c>
       <c r="D40" t="n">
-        <v>2.5</v>
+        <v>1.69</v>
       </c>
       <c r="E40" t="n">
-        <v>1.16929</v>
+        <v>0.81335</v>
       </c>
       <c r="F40" t="n">
-        <v>0.7565</v>
+        <v>0.7068</v>
       </c>
       <c r="G40" t="n">
         <v>1.7899</v>
       </c>
       <c r="H40" t="n">
-        <v>0.2735</v>
+        <v>0.2632</v>
       </c>
       <c r="I40" t="n">
-        <v>2.33859</v>
+        <v>1.6267</v>
       </c>
       <c r="J40" t="n">
-        <v>0.7565</v>
+        <v>0.7068</v>
       </c>
       <c r="K40" t="n">
         <v>0.08696</v>
       </c>
       <c r="L40" t="n">
-        <v>1.16929</v>
+        <v>0.81335</v>
       </c>
       <c r="M40" t="n">
-        <v>1.09973</v>
+        <v>0.74378</v>
       </c>
       <c r="N40" t="n">
         <v>0.65625</v>
@@ -6497,25 +6491,25 @@
         <v>0.08333</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.938</v>
+        <v>1.25</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.4045</v>
+        <v>1.2295</v>
       </c>
       <c r="AD40" t="n">
         <v>0.844</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.2855</v>
+        <v>1.1705</v>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>2404-16-32</t>
+          <t>2404-16-20</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 1 5/16-12 x 2-11 1/2</t>
+          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 1 5/16-12 x 1 1/4-11 1/2</t>
         </is>
       </c>
       <c r="AH40" t="inlineStr">
@@ -6525,7 +6519,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>2-11 1/2 NPTF</t>
+          <t>1 1/4-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
@@ -6540,17 +6534,17 @@
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>Brennan product drawing 2026-09-05 (OMi-only SKU; absent from Air-Way) ; = OMi WebsitePartsInfo2026 row 515: overall length 2.69, hex 2.5, Side 1 / 2 ID 0.844 / 1.938 (identical to this row) | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex / bores: review table = OMi WebsitePartsInfo2026 (identical values, checked 2026-10-09; first appended from the Brennan product drawing 2026-09-05 - OMi-only size: absent from Air-Way and MS51500G; OMi's data are Brennan's, evidence 2026-09-26 -&gt; one source, ASSUMED); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: two bores - the review-table counterbore CBDIA on its end, D3 through the rest - stepped at the HEX MID-PLANE (user 2026-10-09, Q-2404-BORE: the hole is not the same throughout (from OMi); ASSUMPTION for the step: no depth is published for this size - Air-Way prints none, MS51500G does not list it - Air-Way's 2404 / 2404-L drawings show the step inside the hex (2404-L at its middle), and the 14 two-bore 2404 parts measured 2026-10-01 have it at the hex mid-plane within 0.0005 - ASSUMED)</t>
+          <t>Brennan STEP measured == MS33656J published (VERIFIED) ; bores: OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 513 (= Air-Way D / D1 to rounding) (2026-10-09) | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: two bores - the review-table counterbore CBDIA on its end, D3 through the rest - stepped at the HEX MID-PLANE (user 2026-10-09, Q-2404-BORE: the hole is not the same throughout (from OMi); ASSUMPTION for the step: no depth is published for this size - Air-Way prints none, MS51500G does not list it - Air-Way's 2404 / 2404-L drawings show the step inside the hex (2404-L at its middle), and the 14 two-bore 2404 parts measured 2026-10-01 have it at the hex mid-plane within 0.0005 - ASSUMED)</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>RELEASED 2026-10-09 (Q-2404-BORE): step at the hex mid-plane (was: BLOCKED: CB depth unsourced)</t>
+          <t>2026-10-09 Q-2404-BORE (user, from OMi: the hole is not the same throughout): two bores, JIC 0.844 / pipe 1.25 from OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 513 (= Air-Way D / D1 to rounding); step at the hex mid-plane (Air-Way prints no depth, its drawing shows the step inside the hex)</t>
         </is>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>2404-16-32</t>
+          <t>2404-16-20</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
@@ -6562,67 +6556,70 @@
         <is>
           <t>Trivalent Cr3 Zinc</t>
         </is>
+      </c>
+      <c r="AQ40" t="n">
+        <v>2500</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2404-20-12</t>
+          <t>2404-16-24</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2.23</v>
+        <v>2.51</v>
       </c>
       <c r="C41" t="n">
-        <v>0.97572</v>
+        <v>1.1547</v>
       </c>
       <c r="D41" t="n">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
-        <v>0.51241</v>
+        <v>0.93283</v>
       </c>
       <c r="F41" t="n">
-        <v>0.5457</v>
+        <v>0.7235</v>
       </c>
       <c r="G41" t="n">
         <v>1.7899</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2043</v>
+        <v>0.2765</v>
       </c>
       <c r="I41" t="n">
-        <v>1.02482</v>
+        <v>1.86566</v>
       </c>
       <c r="J41" t="n">
-        <v>0.5457</v>
+        <v>0.7235</v>
       </c>
       <c r="K41" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.08696</v>
       </c>
       <c r="L41" t="n">
-        <v>0.51241</v>
+        <v>0.93283</v>
       </c>
       <c r="M41" t="n">
-        <v>0.45527</v>
+        <v>0.86326</v>
       </c>
       <c r="N41" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="O41" t="n">
         <v>0.125</v>
       </c>
       <c r="P41" t="n">
-        <v>0.4316</v>
+        <v>0.4365</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.753</v>
+        <v>0.5965</v>
       </c>
       <c r="R41" t="n">
-        <v>0.1288</v>
+        <v>0.1292</v>
       </c>
       <c r="S41" t="n">
-        <v>0.2382</v>
+        <v>0.1858</v>
       </c>
       <c r="T41" t="n">
         <v>60</v>
@@ -6631,13 +6628,13 @@
         <v>37</v>
       </c>
       <c r="V41" t="n">
-        <v>1.625</v>
+        <v>1.3125</v>
       </c>
       <c r="W41" t="n">
         <v>0.08333</v>
       </c>
       <c r="X41" t="n">
-        <v>0.7986</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="Y41" t="n">
         <v>0.04511</v>
@@ -6649,25 +6646,25 @@
         <v>0.08333</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.719</v>
+        <v>1.5</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.011</v>
+        <v>1.2995</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.078</v>
+        <v>0.844</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.219</v>
+        <v>1.2105</v>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>2404-20-12</t>
+          <t>2404-16-24</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 1 5/8-12 x 3/4-14</t>
+          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 1 5/16-12 x 1 1/2-11 1/2</t>
         </is>
       </c>
       <c r="AH41" t="inlineStr">
@@ -6677,12 +6674,12 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF</t>
+          <t>1 1/2-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>1 5/8-12</t>
+          <t>1 5/16-12</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -6692,17 +6689,17 @@
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>Brennan STEP measured == MS33656J published (VERIFIED) ; bores: OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 516 (= Air-Way D / D1 to rounding) (2026-10-09) | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: two bores - the review-table counterbore CBDIA on its end, D3 through the rest - stepped at the HEX MID-PLANE (user 2026-10-09, Q-2404-BORE: the hole is not the same throughout (from OMi); ASSUMPTION for the step: no depth is published for this size - Air-Way prints none, MS51500G does not list it - Air-Way's 2404 / 2404-L drawings show the step inside the hex (2404-L at its middle), and the 14 two-bore 2404 parts measured 2026-10-01 have it at the hex mid-plane within 0.0005 - ASSUMED)</t>
+          <t>Brennan STEP measured == MS33656J published (VERIFIED) ; bores: OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 514 (= Air-Way D / D1 to rounding) (2026-10-09) | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: two bores - the review-table counterbore CBDIA on its end, D3 through the rest - stepped at the HEX MID-PLANE (user 2026-10-09, Q-2404-BORE: the hole is not the same throughout (from OMi); ASSUMPTION for the step: no depth is published for this size - Air-Way prints none, MS51500G does not list it - Air-Way's 2404 / 2404-L drawings show the step inside the hex (2404-L at its middle), and the 14 two-bore 2404 parts measured 2026-10-01 have it at the hex mid-plane within 0.0005 - ASSUMED)</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>2026-10-09 Q-2404-BORE (user, from OMi: the hole is not the same throughout): two bores, JIC 1.078 / pipe 0.719 from OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 516 (= Air-Way D / D1 to rounding); step at the hex mid-plane (Air-Way prints no depth, its drawing shows the step inside the hex)</t>
+          <t>RESOLVED: L=2.51 - Air-Way+Brennan drawing agree on 2.51 (Parker 2.50 outvoted 2-1, 2026-09-05) ; 2026-10-09 Q-2404-BORE (user, from OMi: the hole is not the same throughout): two bores, JIC 0.844 / pipe 1.5 from OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 514 (= Air-Way D / D1 to rounding); step at the hex mid-plane (Air-Way prints no depth, its drawing shows the step inside the hex) | DataStatus VERIFIED -&gt; ASSUMED: counterbore depth unpublished: step at the hex mid-plane (Brennan-measured rule, single manufacturer)</t>
         </is>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>2404-20-12</t>
+          <t>2404-16-24</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
@@ -6716,68 +6713,68 @@
         </is>
       </c>
       <c r="AQ41" t="n">
-        <v>2500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2404-20-16</t>
+          <t>2404-16-32</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2.42</v>
+        <v>2.69</v>
       </c>
       <c r="C42" t="n">
-        <v>0.97572</v>
+        <v>1.44338</v>
       </c>
       <c r="D42" t="n">
-        <v>1.69</v>
+        <v>2.5</v>
       </c>
       <c r="E42" t="n">
-        <v>0.6415999999999999</v>
+        <v>1.16929</v>
       </c>
       <c r="F42" t="n">
-        <v>0.6828</v>
+        <v>0.7565</v>
       </c>
       <c r="G42" t="n">
         <v>1.7899</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2572</v>
+        <v>0.2735</v>
       </c>
       <c r="I42" t="n">
-        <v>1.2832</v>
+        <v>2.33859</v>
       </c>
       <c r="J42" t="n">
-        <v>0.6828</v>
+        <v>0.7565</v>
       </c>
       <c r="K42" t="n">
         <v>0.08696</v>
       </c>
       <c r="L42" t="n">
-        <v>0.6415999999999999</v>
+        <v>1.16929</v>
       </c>
       <c r="M42" t="n">
-        <v>0.57203</v>
+        <v>1.09973</v>
       </c>
       <c r="N42" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="O42" t="n">
         <v>0.125</v>
       </c>
       <c r="P42" t="n">
-        <v>0.4316</v>
+        <v>0.4365</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.753</v>
+        <v>0.5965</v>
       </c>
       <c r="R42" t="n">
-        <v>0.1288</v>
+        <v>0.1292</v>
       </c>
       <c r="S42" t="n">
-        <v>0.2382</v>
+        <v>0.1858</v>
       </c>
       <c r="T42" t="n">
         <v>60</v>
@@ -6786,13 +6783,13 @@
         <v>37</v>
       </c>
       <c r="V42" t="n">
-        <v>1.625</v>
+        <v>1.3125</v>
       </c>
       <c r="W42" t="n">
         <v>0.08333</v>
       </c>
       <c r="X42" t="n">
-        <v>0.7986</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="Y42" t="n">
         <v>0.04511</v>
@@ -6804,25 +6801,25 @@
         <v>0.08333</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.9379999999999999</v>
+        <v>1.938</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.201</v>
+        <v>1.4045</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.078</v>
+        <v>0.844</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.219</v>
+        <v>1.2855</v>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>2404-20-16</t>
+          <t>2404-16-32</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 1 5/8-12 x 1-11 1/2</t>
+          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 1 5/16-12 x 2-11 1/2</t>
         </is>
       </c>
       <c r="AH42" t="inlineStr">
@@ -6832,12 +6829,12 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF</t>
+          <t>2-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>1 5/8-12</t>
+          <t>1 5/16-12</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -6847,17 +6844,17 @@
       </c>
       <c r="AL42" t="inlineStr">
         <is>
-          <t>Brennan STEP measured == MS33656J published (VERIFIED) ; bores: OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 517 (= Air-Way D / D1 to rounding) (2026-10-09) | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: two bores - the review-table counterbore CBDIA on its end, D3 through the rest - stepped at the HEX MID-PLANE (user 2026-10-09, Q-2404-BORE: the hole is not the same throughout (from OMi); ASSUMPTION for the step: no depth is published for this size - Air-Way prints none, MS51500G does not list it - Air-Way's 2404 / 2404-L drawings show the step inside the hex (2404-L at its middle), and the 14 two-bore 2404 parts measured 2026-10-01 have it at the hex mid-plane within 0.0005 - ASSUMED)</t>
+          <t>Brennan product drawing 2026-09-05 (OMi-only SKU; absent from Air-Way) ; = OMi WebsitePartsInfo2026 row 515: overall length 2.69, hex 2.5, Side 1 / 2 ID 0.844 / 1.938 (identical to this row) | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex / bores: review table = OMi WebsitePartsInfo2026 (identical values, checked 2026-10-09; first appended from the Brennan product drawing 2026-09-05 - OMi-only size: absent from Air-Way and MS51500G; OMi's data are Brennan's, evidence 2026-09-26 -&gt; one source, ASSUMED); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: two bores - the review-table counterbore CBDIA on its end, D3 through the rest - stepped at the HEX MID-PLANE (user 2026-10-09, Q-2404-BORE: the hole is not the same throughout (from OMi); ASSUMPTION for the step: no depth is published for this size - Air-Way prints none, MS51500G does not list it - Air-Way's 2404 / 2404-L drawings show the step inside the hex (2404-L at its middle), and the 14 two-bore 2404 parts measured 2026-10-01 have it at the hex mid-plane within 0.0005 - ASSUMED)</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>2026-10-09 Q-2404-BORE (user, from OMi: the hole is not the same throughout): two bores, JIC 1.078 / pipe 0.938 from OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 517 (= Air-Way D / D1 to rounding); step at the hex mid-plane (Air-Way prints no depth, its drawing shows the step inside the hex)</t>
+          <t>RELEASED 2026-10-09 (Q-2404-BORE): step at the hex mid-plane (was: BLOCKED: CB depth unsourced)</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>2404-20-16</t>
+          <t>2404-16-32</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
@@ -6869,52 +6866,49 @@
         <is>
           <t>Trivalent Cr3 Zinc</t>
         </is>
-      </c>
-      <c r="AQ42" t="n">
-        <v>2500</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2404-20-20</t>
+          <t>2404-20-12</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2.45</v>
+        <v>2.23</v>
       </c>
       <c r="C43" t="n">
-        <v>0.97428</v>
+        <v>0.97572</v>
       </c>
       <c r="D43" t="n">
-        <v>1.6875</v>
+        <v>1.69</v>
       </c>
       <c r="E43" t="n">
-        <v>0.81335</v>
+        <v>0.51241</v>
       </c>
       <c r="F43" t="n">
-        <v>0.7068</v>
+        <v>0.5457</v>
       </c>
       <c r="G43" t="n">
         <v>1.7899</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2632</v>
+        <v>0.2043</v>
       </c>
       <c r="I43" t="n">
-        <v>1.6267</v>
+        <v>1.02482</v>
       </c>
       <c r="J43" t="n">
-        <v>0.7068</v>
+        <v>0.5457</v>
       </c>
       <c r="K43" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="L43" t="n">
-        <v>0.81335</v>
+        <v>0.51241</v>
       </c>
       <c r="M43" t="n">
-        <v>0.74378</v>
+        <v>0.45527</v>
       </c>
       <c r="N43" t="n">
         <v>0.8125</v>
@@ -6959,25 +6953,25 @@
         <v>0.08333</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.25</v>
+        <v>0.719</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.2</v>
+        <v>1.011</v>
       </c>
       <c r="AD43" t="n">
         <v>1.078</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.25</v>
+        <v>1.219</v>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>2404-20-20</t>
+          <t>2404-20-12</t>
         </is>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 1 5/8-12 x 1 1/4-11 1/2</t>
+          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 1 5/8-12 x 3/4-14</t>
         </is>
       </c>
       <c r="AH43" t="inlineStr">
@@ -6987,7 +6981,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPTF</t>
+          <t>3/4-14 NPTF</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -6997,17 +6991,22 @@
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AL43" t="inlineStr">
         <is>
-          <t>Brennan STEP measured == MS33656J published (VERIFIED) | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: through passage = the smaller of D / D1, the end carrying the larger counterbored to depth S (MS51500G Note 5 and its S column; hand-made 2404 table CBCUT columns)</t>
+          <t>Brennan STEP measured == MS33656J published (VERIFIED) ; bores: OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 516 (= Air-Way D / D1 to rounding) (2026-10-09) | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: two bores - the review-table counterbore CBDIA on its end, D3 through the rest - stepped at the HEX MID-PLANE (user 2026-10-09, Q-2404-BORE: the hole is not the same throughout (from OMi); ASSUMPTION for the step: no depth is published for this size - Air-Way prints none, MS51500G does not list it - Air-Way's 2404 / 2404-L drawings show the step inside the hex (2404-L at its middle), and the 14 two-bore 2404 parts measured 2026-10-01 have it at the hex mid-plane within 0.0005 - ASSUMED)</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>2026-10-09 Q-2404-BORE (user, from OMi: the hole is not the same throughout): two bores, JIC 1.078 / pipe 0.719 from OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 516 (= Air-Way D / D1 to rounding); step at the hex mid-plane (Air-Way prints no depth, its drawing shows the step inside the hex)</t>
         </is>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>2404-20-20</t>
+          <t>2404-20-12</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
@@ -7027,44 +7026,44 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2404-20-24</t>
+          <t>2404-20-16</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="C44" t="n">
-        <v>1.1547</v>
+        <v>0.97572</v>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="E44" t="n">
-        <v>0.93283</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="F44" t="n">
-        <v>0.7235</v>
+        <v>0.6828</v>
       </c>
       <c r="G44" t="n">
         <v>1.7899</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2765</v>
+        <v>0.2572</v>
       </c>
       <c r="I44" t="n">
-        <v>1.86566</v>
+        <v>1.2832</v>
       </c>
       <c r="J44" t="n">
-        <v>0.7235</v>
+        <v>0.6828</v>
       </c>
       <c r="K44" t="n">
         <v>0.08696</v>
       </c>
       <c r="L44" t="n">
-        <v>0.93283</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>0.86326</v>
+        <v>0.57203</v>
       </c>
       <c r="N44" t="n">
         <v>0.8125</v>
@@ -7109,25 +7108,25 @@
         <v>0.08333</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.5</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.296</v>
+        <v>1.201</v>
       </c>
       <c r="AD44" t="n">
         <v>1.078</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.254</v>
+        <v>1.219</v>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>2404-20-24</t>
+          <t>2404-20-16</t>
         </is>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 1 5/8-12 x 1 1/2-11 1/2</t>
+          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 1 5/8-12 x 1-11 1/2</t>
         </is>
       </c>
       <c r="AH44" t="inlineStr">
@@ -7137,7 +7136,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>1 1/2-11 1/2 NPTF</t>
+          <t>1-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -7152,17 +7151,17 @@
       </c>
       <c r="AL44" t="inlineStr">
         <is>
-          <t>Brennan STEP measured == MS33656J published (VERIFIED) ; bores: OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 519 (= Air-Way D / D1 to rounding) (2026-10-09) | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: two bores - the review-table counterbore CBDIA on its end, D3 through the rest - stepped at the HEX MID-PLANE (user 2026-10-09, Q-2404-BORE: the hole is not the same throughout (from OMi); ASSUMPTION for the step: no depth is published for this size - Air-Way prints none, MS51500G does not list it - Air-Way's 2404 / 2404-L drawings show the step inside the hex (2404-L at its middle), and the 14 two-bore 2404 parts measured 2026-10-01 have it at the hex mid-plane within 0.0005 - ASSUMED)</t>
+          <t>Brennan STEP measured == MS33656J published (VERIFIED) ; bores: OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 517 (= Air-Way D / D1 to rounding) (2026-10-09) | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: two bores - the review-table counterbore CBDIA on its end, D3 through the rest - stepped at the HEX MID-PLANE (user 2026-10-09, Q-2404-BORE: the hole is not the same throughout (from OMi); ASSUMPTION for the step: no depth is published for this size - Air-Way prints none, MS51500G does not list it - Air-Way's 2404 / 2404-L drawings show the step inside the hex (2404-L at its middle), and the 14 two-bore 2404 parts measured 2026-10-01 have it at the hex mid-plane within 0.0005 - ASSUMED)</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>2026-10-09 Q-2404-BORE (user, from OMi: the hole is not the same throughout): two bores, JIC 1.078 / pipe 1.5 from OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 519 (= Air-Way D / D1 to rounding); step at the hex mid-plane (Air-Way prints no depth, its drawing shows the step inside the hex)</t>
+          <t>2026-10-09 Q-2404-BORE (user, from OMi: the hole is not the same throughout): two bores, JIC 1.078 / pipe 0.938 from OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 517 (= Air-Way D / D1 to rounding); step at the hex mid-plane (Air-Way prints no depth, its drawing shows the step inside the hex)</t>
         </is>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>2404-20-24</t>
+          <t>2404-20-16</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
@@ -7176,50 +7175,50 @@
         </is>
       </c>
       <c r="AQ44" t="n">
-        <v>2000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2404-20-32</t>
+          <t>2404-20-20</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.74</v>
+        <v>2.45</v>
       </c>
       <c r="C45" t="n">
-        <v>1.44338</v>
+        <v>0.97428</v>
       </c>
       <c r="D45" t="n">
-        <v>2.5</v>
+        <v>1.6875</v>
       </c>
       <c r="E45" t="n">
-        <v>1.16929</v>
+        <v>0.81335</v>
       </c>
       <c r="F45" t="n">
-        <v>0.7565</v>
+        <v>0.7068</v>
       </c>
       <c r="G45" t="n">
         <v>1.7899</v>
       </c>
       <c r="H45" t="n">
-        <v>0.2735</v>
+        <v>0.2632</v>
       </c>
       <c r="I45" t="n">
-        <v>2.33859</v>
+        <v>1.6267</v>
       </c>
       <c r="J45" t="n">
-        <v>0.7565</v>
+        <v>0.7068</v>
       </c>
       <c r="K45" t="n">
         <v>0.08696</v>
       </c>
       <c r="L45" t="n">
-        <v>1.16929</v>
+        <v>0.81335</v>
       </c>
       <c r="M45" t="n">
-        <v>1.09973</v>
+        <v>0.74378</v>
       </c>
       <c r="N45" t="n">
         <v>0.8125</v>
@@ -7264,25 +7263,25 @@
         <v>0.08333</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.937</v>
+        <v>1.25</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.406</v>
+        <v>1.2</v>
       </c>
       <c r="AD45" t="n">
         <v>1.078</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.334</v>
+        <v>1.25</v>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>2404-20-32</t>
+          <t>2404-20-20</t>
         </is>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 1 5/8-12 x 2-11 1/2</t>
+          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 1 5/8-12 x 1 1/4-11 1/2</t>
         </is>
       </c>
       <c r="AH45" t="inlineStr">
@@ -7292,7 +7291,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>2-11 1/2 NPTF</t>
+          <t>1 1/4-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
@@ -7302,22 +7301,17 @@
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>Brennan STEP measured == MS33656J published (VERIFIED) ; bores: OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 520 (= Air-Way D / D1 to rounding) (2026-10-09) | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: two bores - the review-table counterbore CBDIA on its end, D3 through the rest - stepped at the HEX MID-PLANE (user 2026-10-09, Q-2404-BORE: the hole is not the same throughout (from OMi); ASSUMPTION for the step: no depth is published for this size - Air-Way prints none, MS51500G does not list it - Air-Way's 2404 / 2404-L drawings show the step inside the hex (2404-L at its middle), and the 14 two-bore 2404 parts measured 2026-10-01 have it at the hex mid-plane within 0.0005 - ASSUMED)</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>2026-10-09: overall length 2.74 from OMi (row 520; was 2.73, question 26 / OMi first) ; 2026-10-09 Q-2404-BORE (user, from OMi: the hole is not the same throughout): two bores, JIC 1.078 / pipe 1.937 from OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 520 (= Air-Way D / D1 to rounding); step at the hex mid-plane (Air-Way prints no depth, its drawing shows the step inside the hex)</t>
+          <t>Brennan STEP measured == MS33656J published (VERIFIED) | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: through passage = the smaller of D / D1, the end carrying the larger counterbored to depth S (MS51500G Note 5 and its S column; hand-made 2404 table CBCUT columns)</t>
         </is>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>2404-20-32</t>
+          <t>2404-20-20</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
@@ -7331,17 +7325,17 @@
         </is>
       </c>
       <c r="AQ45" t="n">
-        <v>1500</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2404-24-16</t>
+          <t>2404-20-24</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="C46" t="n">
         <v>1.1547</v>
@@ -7350,49 +7344,49 @@
         <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.93283</v>
       </c>
       <c r="F46" t="n">
-        <v>0.6828</v>
+        <v>0.7235</v>
       </c>
       <c r="G46" t="n">
         <v>1.7899</v>
       </c>
       <c r="H46" t="n">
-        <v>0.2572</v>
+        <v>0.2765</v>
       </c>
       <c r="I46" t="n">
-        <v>1.2832</v>
+        <v>1.86566</v>
       </c>
       <c r="J46" t="n">
-        <v>0.6828</v>
+        <v>0.7235</v>
       </c>
       <c r="K46" t="n">
         <v>0.08696</v>
       </c>
       <c r="L46" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.93283</v>
       </c>
       <c r="M46" t="n">
-        <v>0.57203</v>
+        <v>0.86326</v>
       </c>
       <c r="N46" t="n">
-        <v>0.9375</v>
+        <v>0.8125</v>
       </c>
       <c r="O46" t="n">
         <v>0.125</v>
       </c>
       <c r="P46" t="n">
-        <v>0.5454</v>
+        <v>0.4316</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.753</v>
       </c>
       <c r="R46" t="n">
-        <v>0.1298</v>
+        <v>0.1288</v>
       </c>
       <c r="S46" t="n">
-        <v>0.2482</v>
+        <v>0.2382</v>
       </c>
       <c r="T46" t="n">
         <v>60</v>
@@ -7401,13 +7395,13 @@
         <v>37</v>
       </c>
       <c r="V46" t="n">
-        <v>1.875</v>
+        <v>1.625</v>
       </c>
       <c r="W46" t="n">
         <v>0.08333</v>
       </c>
       <c r="X46" t="n">
-        <v>0.9234</v>
+        <v>0.7986</v>
       </c>
       <c r="Y46" t="n">
         <v>0.04511</v>
@@ -7419,25 +7413,25 @@
         <v>0.08333</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.9379999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.2385</v>
+        <v>1.296</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.312</v>
+        <v>1.078</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.3815</v>
+        <v>1.254</v>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>2404-24-16</t>
+          <t>2404-20-24</t>
         </is>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 1 7/8-12 x 1-11 1/2</t>
+          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 1 5/8-12 x 1 1/2-11 1/2</t>
         </is>
       </c>
       <c r="AH46" t="inlineStr">
@@ -7447,12 +7441,12 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF</t>
+          <t>1 1/2-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>1 7/8-12</t>
+          <t>1 5/8-12</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -7462,17 +7456,17 @@
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>Brennan STEP measured == MS33656J published (VERIFIED) ; bores: OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 522 (= Air-Way D / D1 to rounding) (2026-10-09) | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: two bores - the review-table counterbore CBDIA on its end, D3 through the rest - stepped at the HEX MID-PLANE (user 2026-10-09, Q-2404-BORE: the hole is not the same throughout (from OMi); ASSUMPTION for the step: no depth is published for this size - Air-Way prints none, MS51500G does not list it - Air-Way's 2404 / 2404-L drawings show the step inside the hex (2404-L at its middle), and the 14 two-bore 2404 parts measured 2026-10-01 have it at the hex mid-plane within 0.0005 - ASSUMED)</t>
+          <t>Brennan STEP measured == MS33656J published (VERIFIED) ; bores: OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 519 (= Air-Way D / D1 to rounding) (2026-10-09) | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: two bores - the review-table counterbore CBDIA on its end, D3 through the rest - stepped at the HEX MID-PLANE (user 2026-10-09, Q-2404-BORE: the hole is not the same throughout (from OMi); ASSUMPTION for the step: no depth is published for this size - Air-Way prints none, MS51500G does not list it - Air-Way's 2404 / 2404-L drawings show the step inside the hex (2404-L at its middle), and the 14 two-bore 2404 parts measured 2026-10-01 have it at the hex mid-plane within 0.0005 - ASSUMED)</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>2026-10-09 Q-2404-BORE (user, from OMi: the hole is not the same throughout): two bores, JIC 1.312 / pipe 0.938 from OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 522 (= Air-Way D / D1 to rounding); step at the hex mid-plane (Air-Way prints no depth, its drawing shows the step inside the hex)</t>
+          <t>2026-10-09 Q-2404-BORE (user, from OMi: the hole is not the same throughout): two bores, JIC 1.078 / pipe 1.5 from OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 519 (= Air-Way D / D1 to rounding); step at the hex mid-plane (Air-Way prints no depth, its drawing shows the step inside the hex)</t>
         </is>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>2404-24-16</t>
+          <t>2404-20-24</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
@@ -7492,62 +7486,62 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2404-24-20</t>
+          <t>2404-20-32</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2.65</v>
+        <v>2.74</v>
       </c>
       <c r="C47" t="n">
-        <v>1.1547</v>
+        <v>1.44338</v>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E47" t="n">
-        <v>0.81335</v>
+        <v>1.16929</v>
       </c>
       <c r="F47" t="n">
-        <v>0.7068</v>
+        <v>0.7565</v>
       </c>
       <c r="G47" t="n">
         <v>1.7899</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2632</v>
+        <v>0.2735</v>
       </c>
       <c r="I47" t="n">
-        <v>1.6267</v>
+        <v>2.33859</v>
       </c>
       <c r="J47" t="n">
-        <v>0.7068</v>
+        <v>0.7565</v>
       </c>
       <c r="K47" t="n">
         <v>0.08696</v>
       </c>
       <c r="L47" t="n">
-        <v>0.81335</v>
+        <v>1.16929</v>
       </c>
       <c r="M47" t="n">
-        <v>0.74378</v>
+        <v>1.09973</v>
       </c>
       <c r="N47" t="n">
-        <v>0.9375</v>
+        <v>0.8125</v>
       </c>
       <c r="O47" t="n">
         <v>0.125</v>
       </c>
       <c r="P47" t="n">
-        <v>0.5454</v>
+        <v>0.4316</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.753</v>
       </c>
       <c r="R47" t="n">
-        <v>0.1298</v>
+        <v>0.1288</v>
       </c>
       <c r="S47" t="n">
-        <v>0.2482</v>
+        <v>0.2382</v>
       </c>
       <c r="T47" t="n">
         <v>60</v>
@@ -7556,13 +7550,13 @@
         <v>37</v>
       </c>
       <c r="V47" t="n">
-        <v>1.875</v>
+        <v>1.625</v>
       </c>
       <c r="W47" t="n">
         <v>0.08333</v>
       </c>
       <c r="X47" t="n">
-        <v>0.9234</v>
+        <v>0.7986</v>
       </c>
       <c r="Y47" t="n">
         <v>0.04511</v>
@@ -7574,25 +7568,25 @@
         <v>0.08333</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.25</v>
+        <v>1.937</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.2685</v>
+        <v>1.406</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.31</v>
+        <v>1.078</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.3815</v>
+        <v>1.334</v>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>2404-24-20</t>
+          <t>2404-20-32</t>
         </is>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 1 7/8-12 x 1 1/4-11 1/2</t>
+          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 1 5/8-12 x 2-11 1/2</t>
         </is>
       </c>
       <c r="AH47" t="inlineStr">
@@ -7602,12 +7596,12 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPTF</t>
+          <t>2-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>1 7/8-12</t>
+          <t>1 5/8-12</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -7617,17 +7611,17 @@
       </c>
       <c r="AL47" t="inlineStr">
         <is>
-          <t>Brennan STEP measured == MS33656J published (VERIFIED) ; bores: Air-Way D 1.31 / D1 1.25 (user 2026-10-09: "look at airway"; OMi row 523 lists 1.25 / 1.25) (2026-10-09) | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: two bores - the review-table counterbore CBDIA on its end, D3 through the rest - stepped at the HEX MID-PLANE (user 2026-10-09, Q-2404-BORE: the hole is not the same throughout (from OMi); ASSUMPTION for the step: no depth is published for this size - Air-Way prints none, MS51500G does not list it - Air-Way's 2404 / 2404-L drawings show the step inside the hex (2404-L at its middle), and the 14 two-bore 2404 parts measured 2026-10-01 have it at the hex mid-plane within 0.0005 - ASSUMED)</t>
+          <t>Brennan STEP measured == MS33656J published (VERIFIED) ; bores: OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 520 (= Air-Way D / D1 to rounding) (2026-10-09) | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: two bores - the review-table counterbore CBDIA on its end, D3 through the rest - stepped at the HEX MID-PLANE (user 2026-10-09, Q-2404-BORE: the hole is not the same throughout (from OMi); ASSUMPTION for the step: no depth is published for this size - Air-Way prints none, MS51500G does not list it - Air-Way's 2404 / 2404-L drawings show the step inside the hex (2404-L at its middle), and the 14 two-bore 2404 parts measured 2026-10-01 have it at the hex mid-plane within 0.0005 - ASSUMED)</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>RESOLVED: L=2.65 - Air-Way+Brennan drawing agree on 2.65 (Parker 2.66 outvoted 2-1, 2026-09-05) ; 2026-10-09 Q-2404-BORE (user, from OMi: the hole is not the same throughout): two bores, JIC 1.31 / pipe 1.25 from Air-Way D 1.31 / D1 1.25 (user 2026-10-09: "look at airway"; OMi row 523 lists 1.25 / 1.25); step at the hex mid-plane (Air-Way prints no depth, its drawing shows the step inside the hex) | DataStatus VERIFIED -&gt; ASSUMED: counterbore depth unpublished: step at the hex mid-plane (Brennan-measured rule, single manufacturer)</t>
+          <t>2026-10-09: overall length 2.74 from OMi (row 520; was 2.73, question 26 / OMi first) ; 2026-10-09 Q-2404-BORE (user, from OMi: the hole is not the same throughout): two bores, JIC 1.078 / pipe 1.937 from OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 520 (= Air-Way D / D1 to rounding); step at the hex mid-plane (Air-Way prints no depth, its drawing shows the step inside the hex)</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>2404-24-20</t>
+          <t>2404-20-32</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
@@ -7641,17 +7635,17 @@
         </is>
       </c>
       <c r="AQ47" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2404-24-24</t>
+          <t>2404-24-16</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="C48" t="n">
         <v>1.1547</v>
@@ -7660,31 +7654,31 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>0.93283</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="F48" t="n">
-        <v>0.7235</v>
+        <v>0.6828</v>
       </c>
       <c r="G48" t="n">
         <v>1.7899</v>
       </c>
       <c r="H48" t="n">
-        <v>0.2765</v>
+        <v>0.2572</v>
       </c>
       <c r="I48" t="n">
-        <v>1.86566</v>
+        <v>1.2832</v>
       </c>
       <c r="J48" t="n">
-        <v>0.7235</v>
+        <v>0.6828</v>
       </c>
       <c r="K48" t="n">
         <v>0.08696</v>
       </c>
       <c r="L48" t="n">
-        <v>0.93283</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="M48" t="n">
-        <v>0.86326</v>
+        <v>0.57203</v>
       </c>
       <c r="N48" t="n">
         <v>0.9375</v>
@@ -7729,25 +7723,25 @@
         <v>0.08333</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.5</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.27</v>
+        <v>1.2385</v>
       </c>
       <c r="AD48" t="n">
         <v>1.312</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.41</v>
+        <v>1.3815</v>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>2404-24-24</t>
+          <t>2404-24-16</t>
         </is>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 1 7/8-12 x 1 1/2-11 1/2</t>
+          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 1 7/8-12 x 1-11 1/2</t>
         </is>
       </c>
       <c r="AH48" t="inlineStr">
@@ -7757,7 +7751,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>1 1/2-11 1/2 NPTF</t>
+          <t>1-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -7767,17 +7761,22 @@
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>Brennan STEP measured == MS33656J published (VERIFIED) | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: through passage = the smaller of D / D1, the end carrying the larger counterbored to depth S (MS51500G Note 5 and its S column; hand-made 2404 table CBCUT columns)</t>
+          <t>Brennan STEP measured == MS33656J published (VERIFIED) ; bores: OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 522 (= Air-Way D / D1 to rounding) (2026-10-09) | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: two bores - the review-table counterbore CBDIA on its end, D3 through the rest - stepped at the HEX MID-PLANE (user 2026-10-09, Q-2404-BORE: the hole is not the same throughout (from OMi); ASSUMPTION for the step: no depth is published for this size - Air-Way prints none, MS51500G does not list it - Air-Way's 2404 / 2404-L drawings show the step inside the hex (2404-L at its middle), and the 14 two-bore 2404 parts measured 2026-10-01 have it at the hex mid-plane within 0.0005 - ASSUMED)</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>2026-10-09 Q-2404-BORE (user, from OMi: the hole is not the same throughout): two bores, JIC 1.312 / pipe 0.938 from OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 522 (= Air-Way D / D1 to rounding); step at the hex mid-plane (Air-Way prints no depth, its drawing shows the step inside the hex)</t>
         </is>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>2404-24-24</t>
+          <t>2404-24-16</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
@@ -7797,44 +7796,44 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2404-24-32</t>
+          <t>2404-24-20</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2.86</v>
+        <v>2.65</v>
       </c>
       <c r="C49" t="n">
-        <v>1.51843</v>
+        <v>1.1547</v>
       </c>
       <c r="D49" t="n">
-        <v>2.63</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>1.16929</v>
+        <v>0.81335</v>
       </c>
       <c r="F49" t="n">
-        <v>0.7565</v>
+        <v>0.7068</v>
       </c>
       <c r="G49" t="n">
         <v>1.7899</v>
       </c>
       <c r="H49" t="n">
-        <v>0.2735</v>
+        <v>0.2632</v>
       </c>
       <c r="I49" t="n">
-        <v>2.33859</v>
+        <v>1.6267</v>
       </c>
       <c r="J49" t="n">
-        <v>0.7565</v>
+        <v>0.7068</v>
       </c>
       <c r="K49" t="n">
         <v>0.08696</v>
       </c>
       <c r="L49" t="n">
-        <v>1.16929</v>
+        <v>0.81335</v>
       </c>
       <c r="M49" t="n">
-        <v>1.09973</v>
+        <v>0.74378</v>
       </c>
       <c r="N49" t="n">
         <v>0.9375</v>
@@ -7879,25 +7878,25 @@
         <v>0.08333</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.938</v>
+        <v>1.25</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.4035</v>
+        <v>1.2685</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.312</v>
+        <v>1.31</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.4565</v>
+        <v>1.3815</v>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>2404-24-32</t>
+          <t>2404-24-20</t>
         </is>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 1 7/8-12 x 2-11 1/2</t>
+          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 1 7/8-12 x 1 1/4-11 1/2</t>
         </is>
       </c>
       <c r="AH49" t="inlineStr">
@@ -7907,7 +7906,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>2-11 1/2 NPTF</t>
+          <t>1 1/4-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -7922,17 +7921,17 @@
       </c>
       <c r="AL49" t="inlineStr">
         <is>
-          <t>Brennan STEP measured == MS33656J published (VERIFIED) ; bores: OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 525 (= Air-Way D / D1 to rounding) (2026-10-09) | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: two bores - the review-table counterbore CBDIA on its end, D3 through the rest - stepped at the HEX MID-PLANE (user 2026-10-09, Q-2404-BORE: the hole is not the same throughout (from OMi); ASSUMPTION for the step: no depth is published for this size - Air-Way prints none, MS51500G does not list it - Air-Way's 2404 / 2404-L drawings show the step inside the hex (2404-L at its middle), and the 14 two-bore 2404 parts measured 2026-10-01 have it at the hex mid-plane within 0.0005 - ASSUMED)</t>
+          <t>Brennan STEP measured == MS33656J published (VERIFIED) ; bores: Air-Way D 1.31 / D1 1.25 (user 2026-10-09: "look at airway"; OMi row 523 lists 1.25 / 1.25) (2026-10-09) | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: two bores - the review-table counterbore CBDIA on its end, D3 through the rest - stepped at the HEX MID-PLANE (user 2026-10-09, Q-2404-BORE: the hole is not the same throughout (from OMi); ASSUMPTION for the step: no depth is published for this size - Air-Way prints none, MS51500G does not list it - Air-Way's 2404 / 2404-L drawings show the step inside the hex (2404-L at its middle), and the 14 two-bore 2404 parts measured 2026-10-01 have it at the hex mid-plane within 0.0005 - ASSUMED)</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>2026-10-09 Q-2404-BORE (user, from OMi: the hole is not the same throughout): two bores, JIC 1.312 / pipe 1.938 from OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 525 (= Air-Way D / D1 to rounding); step at the hex mid-plane (Air-Way prints no depth, its drawing shows the step inside the hex)</t>
+          <t>RESOLVED: L=2.65 - Air-Way+Brennan drawing agree on 2.65 (Parker 2.66 outvoted 2-1, 2026-09-05) ; 2026-10-09 Q-2404-BORE (user, from OMi: the hole is not the same throughout): two bores, JIC 1.31 / pipe 1.25 from Air-Way D 1.31 / D1 1.25 (user 2026-10-09: "look at airway"; OMi row 523 lists 1.25 / 1.25); step at the hex mid-plane (Air-Way prints no depth, its drawing shows the step inside the hex) | DataStatus VERIFIED -&gt; ASSUMED: counterbore depth unpublished: step at the hex mid-plane (Brennan-measured rule, single manufacturer)</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>2404-24-32</t>
+          <t>2404-24-20</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
@@ -7946,68 +7945,68 @@
         </is>
       </c>
       <c r="AQ49" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2404-32-20</t>
+          <t>2404-24-24</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3.05</v>
+        <v>2.68</v>
       </c>
       <c r="C50" t="n">
-        <v>1.51554</v>
+        <v>1.1547</v>
       </c>
       <c r="D50" t="n">
-        <v>2.625</v>
+        <v>2</v>
       </c>
       <c r="E50" t="n">
-        <v>0.81335</v>
+        <v>0.93283</v>
       </c>
       <c r="F50" t="n">
-        <v>0.7068</v>
+        <v>0.7235</v>
       </c>
       <c r="G50" t="n">
         <v>1.7899</v>
       </c>
       <c r="H50" t="n">
-        <v>0.2632</v>
+        <v>0.2765</v>
       </c>
       <c r="I50" t="n">
-        <v>1.6267</v>
+        <v>1.86566</v>
       </c>
       <c r="J50" t="n">
-        <v>0.7068</v>
+        <v>0.7235</v>
       </c>
       <c r="K50" t="n">
         <v>0.08696</v>
       </c>
       <c r="L50" t="n">
-        <v>0.81335</v>
+        <v>0.93283</v>
       </c>
       <c r="M50" t="n">
-        <v>0.74378</v>
+        <v>0.86326</v>
       </c>
       <c r="N50" t="n">
-        <v>1.25</v>
+        <v>0.9375</v>
       </c>
       <c r="O50" t="n">
         <v>0.125</v>
       </c>
       <c r="P50" t="n">
-        <v>0.7124</v>
+        <v>0.5454</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.19</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="R50" t="n">
-        <v>0.1292</v>
+        <v>0.1298</v>
       </c>
       <c r="S50" t="n">
-        <v>0.3318</v>
+        <v>0.2482</v>
       </c>
       <c r="T50" t="n">
         <v>60</v>
@@ -8016,13 +8015,13 @@
         <v>37</v>
       </c>
       <c r="V50" t="n">
-        <v>2.5</v>
+        <v>1.875</v>
       </c>
       <c r="W50" t="n">
         <v>0.08333</v>
       </c>
       <c r="X50" t="n">
-        <v>1.1734</v>
+        <v>0.9234</v>
       </c>
       <c r="Y50" t="n">
         <v>0.04511</v>
@@ -8034,25 +8033,25 @@
         <v>0.08333</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.3435</v>
+        <v>1.27</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.781</v>
+        <v>1.312</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.7065</v>
+        <v>1.41</v>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>2404-32-20</t>
+          <t>2404-24-24</t>
         </is>
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 2 1/2-12 x 1 1/4-11 1/2</t>
+          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 1 7/8-12 x 1 1/2-11 1/2</t>
         </is>
       </c>
       <c r="AH50" t="inlineStr">
@@ -8062,32 +8061,27 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPTF</t>
+          <t>1 1/2-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>2 1/2-12</t>
+          <t>1 7/8-12</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AL50" t="inlineStr">
         <is>
-          <t>Brennan product drawing 2026-09-05 (OMi-only SKU; absent from Air-Way) ; = OMi WebsitePartsInfo2026 row 526: overall length 3.05, hex 2.625, Side 1 / 2 ID 1.781 / 1.25 (identical to this row) | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex / bores: review table = OMi WebsitePartsInfo2026 (identical values, checked 2026-10-09; first appended from the Brennan product drawing 2026-09-05 - OMi-only size: absent from Air-Way and MS51500G; OMi's data are Brennan's, evidence 2026-09-26 -&gt; one source, ASSUMED); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: two bores - the review-table counterbore CBDIA on its end, D3 through the rest - stepped at the HEX MID-PLANE (user 2026-10-09, Q-2404-BORE: the hole is not the same throughout (from OMi); ASSUMPTION for the step: no depth is published for this size - Air-Way prints none, MS51500G does not list it - Air-Way's 2404 / 2404-L drawings show the step inside the hex (2404-L at its middle), and the 14 two-bore 2404 parts measured 2026-10-01 have it at the hex mid-plane within 0.0005 - ASSUMED)</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>RELEASED 2026-10-09 (Q-2404-BORE): step at the hex mid-plane (was: BLOCKED: CB depth unsourced)</t>
+          <t>Brennan STEP measured == MS33656J published (VERIFIED) | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: through passage = the smaller of D / D1, the end carrying the larger counterbored to depth S (MS51500G Note 5 and its S column; hand-made 2404 table CBCUT columns)</t>
         </is>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>2404-32-20</t>
+          <t>2404-24-24</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
@@ -8099,16 +8093,19 @@
         <is>
           <t>Trivalent Cr3 Zinc</t>
         </is>
+      </c>
+      <c r="AQ50" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2404-32-24</t>
+          <t>2404-24-32</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3.08</v>
+        <v>2.86</v>
       </c>
       <c r="C51" t="n">
         <v>1.51843</v>
@@ -8117,49 +8114,49 @@
         <v>2.63</v>
       </c>
       <c r="E51" t="n">
-        <v>0.93283</v>
+        <v>1.16929</v>
       </c>
       <c r="F51" t="n">
-        <v>0.7235</v>
+        <v>0.7565</v>
       </c>
       <c r="G51" t="n">
         <v>1.7899</v>
       </c>
       <c r="H51" t="n">
-        <v>0.2765</v>
+        <v>0.2735</v>
       </c>
       <c r="I51" t="n">
-        <v>1.86566</v>
+        <v>2.33859</v>
       </c>
       <c r="J51" t="n">
-        <v>0.7235</v>
+        <v>0.7565</v>
       </c>
       <c r="K51" t="n">
         <v>0.08696</v>
       </c>
       <c r="L51" t="n">
-        <v>0.93283</v>
+        <v>1.16929</v>
       </c>
       <c r="M51" t="n">
-        <v>0.86326</v>
+        <v>1.09973</v>
       </c>
       <c r="N51" t="n">
-        <v>1.25</v>
+        <v>0.9375</v>
       </c>
       <c r="O51" t="n">
         <v>0.125</v>
       </c>
       <c r="P51" t="n">
-        <v>0.7124</v>
+        <v>0.5454</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.19</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="R51" t="n">
-        <v>0.1292</v>
+        <v>0.1298</v>
       </c>
       <c r="S51" t="n">
-        <v>0.3318</v>
+        <v>0.2482</v>
       </c>
       <c r="T51" t="n">
         <v>60</v>
@@ -8168,13 +8165,13 @@
         <v>37</v>
       </c>
       <c r="V51" t="n">
-        <v>2.5</v>
+        <v>1.875</v>
       </c>
       <c r="W51" t="n">
         <v>0.08333</v>
       </c>
       <c r="X51" t="n">
-        <v>1.1734</v>
+        <v>0.9234</v>
       </c>
       <c r="Y51" t="n">
         <v>0.04511</v>
@@ -8186,25 +8183,25 @@
         <v>0.08333</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.5</v>
+        <v>1.938</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.3735</v>
+        <v>1.4035</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.781</v>
+        <v>1.312</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.7065</v>
+        <v>1.4565</v>
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>2404-32-24</t>
+          <t>2404-24-32</t>
         </is>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 2 1/2-12 x 1 1/2-11 1/2</t>
+          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 1 7/8-12 x 2-11 1/2</t>
         </is>
       </c>
       <c r="AH51" t="inlineStr">
@@ -8214,12 +8211,12 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>1 1/2-11 1/2 NPTF</t>
+          <t>2-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>2 1/2-12</t>
+          <t>1 7/8-12</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -8229,17 +8226,17 @@
       </c>
       <c r="AL51" t="inlineStr">
         <is>
-          <t>Brennan STEP measured == MS33656J published (VERIFIED) ; bores: OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 527 (= Air-Way D / D1 to rounding) (2026-10-09) | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: two bores - the review-table counterbore CBDIA on its end, D3 through the rest - stepped at the HEX MID-PLANE (user 2026-10-09, Q-2404-BORE: the hole is not the same throughout (from OMi); ASSUMPTION for the step: no depth is published for this size - Air-Way prints none, MS51500G does not list it - Air-Way's 2404 / 2404-L drawings show the step inside the hex (2404-L at its middle), and the 14 two-bore 2404 parts measured 2026-10-01 have it at the hex mid-plane within 0.0005 - ASSUMED)</t>
+          <t>Brennan STEP measured == MS33656J published (VERIFIED) ; bores: OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 525 (= Air-Way D / D1 to rounding) (2026-10-09) | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: two bores - the review-table counterbore CBDIA on its end, D3 through the rest - stepped at the HEX MID-PLANE (user 2026-10-09, Q-2404-BORE: the hole is not the same throughout (from OMi); ASSUMPTION for the step: no depth is published for this size - Air-Way prints none, MS51500G does not list it - Air-Way's 2404 / 2404-L drawings show the step inside the hex (2404-L at its middle), and the 14 two-bore 2404 parts measured 2026-10-01 have it at the hex mid-plane within 0.0005 - ASSUMED)</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>2026-10-09 Q-2404-BORE (user, from OMi: the hole is not the same throughout): two bores, JIC 1.781 / pipe 1.5 from OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 527 (= Air-Way D / D1 to rounding); step at the hex mid-plane (Air-Way prints no depth, its drawing shows the step inside the hex)</t>
+          <t>2026-10-09 Q-2404-BORE (user, from OMi: the hole is not the same throughout): two bores, JIC 1.312 / pipe 1.938 from OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 525 (= Air-Way D / D1 to rounding); step at the hex mid-plane (Air-Way prints no depth, its drawing shows the step inside the hex)</t>
         </is>
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>2404-32-24</t>
+          <t>2404-24-32</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
@@ -8259,11 +8256,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2404-32-32</t>
+          <t>2404-32-20</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3.11</v>
+        <v>3.05</v>
       </c>
       <c r="C52" t="n">
         <v>1.51554</v>
@@ -8272,31 +8269,31 @@
         <v>2.625</v>
       </c>
       <c r="E52" t="n">
-        <v>1.16929</v>
+        <v>0.81335</v>
       </c>
       <c r="F52" t="n">
-        <v>0.7565</v>
+        <v>0.7068</v>
       </c>
       <c r="G52" t="n">
         <v>1.7899</v>
       </c>
       <c r="H52" t="n">
-        <v>0.2735</v>
+        <v>0.2632</v>
       </c>
       <c r="I52" t="n">
-        <v>2.33859</v>
+        <v>1.6267</v>
       </c>
       <c r="J52" t="n">
-        <v>0.7565</v>
+        <v>0.7068</v>
       </c>
       <c r="K52" t="n">
         <v>0.08696</v>
       </c>
       <c r="L52" t="n">
-        <v>1.16929</v>
+        <v>0.81335</v>
       </c>
       <c r="M52" t="n">
-        <v>1.09973</v>
+        <v>0.74378</v>
       </c>
       <c r="N52" t="n">
         <v>1.25</v>
@@ -8341,25 +8338,25 @@
         <v>0.08333</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.938</v>
+        <v>1.25</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.37</v>
+        <v>1.3435</v>
       </c>
       <c r="AD52" t="n">
         <v>1.781</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.74</v>
+        <v>1.7065</v>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>2404-32-32</t>
+          <t>2404-32-20</t>
         </is>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 2 1/2-12 x 2-11 1/2</t>
+          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 2 1/2-12 x 1 1/4-11 1/2</t>
         </is>
       </c>
       <c r="AH52" t="inlineStr">
@@ -8369,7 +8366,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>2-11 1/2 NPTF</t>
+          <t>1 1/4-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
@@ -8379,17 +8376,22 @@
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AL52" t="inlineStr">
         <is>
-          <t>Brennan STEP measured == MS33656J published (VERIFIED) | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: through passage = the smaller of D / D1, the end carrying the larger counterbored to depth S (MS51500G Note 5 and its S column; hand-made 2404 table CBCUT columns)</t>
+          <t>Brennan product drawing 2026-09-05 (OMi-only SKU; absent from Air-Way) ; = OMi WebsitePartsInfo2026 row 526: overall length 3.05, hex 2.625, Side 1 / 2 ID 1.781 / 1.25 (identical to this row) | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex / bores: review table = OMi WebsitePartsInfo2026 (identical values, checked 2026-10-09; first appended from the Brennan product drawing 2026-09-05 - OMi-only size: absent from Air-Way and MS51500G; OMi's data are Brennan's, evidence 2026-09-26 -&gt; one source, ASSUMED); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: two bores - the review-table counterbore CBDIA on its end, D3 through the rest - stepped at the HEX MID-PLANE (user 2026-10-09, Q-2404-BORE: the hole is not the same throughout (from OMi); ASSUMPTION for the step: no depth is published for this size - Air-Way prints none, MS51500G does not list it - Air-Way's 2404 / 2404-L drawings show the step inside the hex (2404-L at its middle), and the 14 two-bore 2404 parts measured 2026-10-01 have it at the hex mid-plane within 0.0005 - ASSUMED)</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>RELEASED 2026-10-09 (Q-2404-BORE): step at the hex mid-plane (was: BLOCKED: CB depth unsourced)</t>
         </is>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>2404-32-32</t>
+          <t>2404-32-20</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -8401,70 +8403,67 @@
         <is>
           <t>Trivalent Cr3 Zinc</t>
         </is>
-      </c>
-      <c r="AQ52" t="n">
-        <v>1500</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2404-40-32</t>
+          <t>2404-32-24</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2.89</v>
+        <v>3.08</v>
       </c>
       <c r="C53" t="n">
-        <v>1.73205</v>
+        <v>1.51843</v>
       </c>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="E53" t="n">
-        <v>1.16929</v>
+        <v>0.93283</v>
       </c>
       <c r="F53" t="n">
-        <v>0.7565</v>
+        <v>0.7235</v>
       </c>
       <c r="G53" t="n">
         <v>1.7899</v>
       </c>
       <c r="H53" t="n">
-        <v>0.2735</v>
+        <v>0.2765</v>
       </c>
       <c r="I53" t="n">
-        <v>2.33859</v>
+        <v>1.86566</v>
       </c>
       <c r="J53" t="n">
-        <v>0.7565</v>
+        <v>0.7235</v>
       </c>
       <c r="K53" t="n">
         <v>0.08696</v>
       </c>
       <c r="L53" t="n">
-        <v>1.16929</v>
+        <v>0.93283</v>
       </c>
       <c r="M53" t="n">
-        <v>1.09973</v>
+        <v>0.86326</v>
       </c>
       <c r="N53" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="O53" t="n">
-        <v>0.14</v>
+        <v>0.125</v>
       </c>
       <c r="P53" t="n">
-        <v>0.7694</v>
+        <v>0.7124</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="R53" t="n">
-        <v>0.0725</v>
+        <v>0.1292</v>
       </c>
       <c r="S53" t="n">
-        <v>0.3185</v>
+        <v>0.3318</v>
       </c>
       <c r="T53" t="n">
         <v>60</v>
@@ -8473,13 +8472,13 @@
         <v>37</v>
       </c>
       <c r="V53" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="W53" t="n">
         <v>0.08333</v>
       </c>
       <c r="X53" t="n">
-        <v>1.1604</v>
+        <v>1.1734</v>
       </c>
       <c r="Y53" t="n">
         <v>0.04511</v>
@@ -8491,25 +8490,25 @@
         <v>0.08333</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.938</v>
+        <v>1.5</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.2925</v>
+        <v>1.3735</v>
       </c>
       <c r="AD53" t="n">
-        <v>2.279</v>
+        <v>1.781</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.5975</v>
+        <v>1.7065</v>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>2404-40-32</t>
+          <t>2404-32-24</t>
         </is>
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 3-12 x 2-11 1/2</t>
+          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 2 1/2-12 x 1 1/2-11 1/2</t>
         </is>
       </c>
       <c r="AH53" t="inlineStr">
@@ -8519,12 +8518,12 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>2-11 1/2 NPTF</t>
+          <t>1 1/2-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>3-12</t>
+          <t>2 1/2-12</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -8534,17 +8533,17 @@
       </c>
       <c r="AL53" t="inlineStr">
         <is>
-          <t>Brennan product drawing 2026-09-05 (OMi-only SKU; absent from Air-Way) ; L matches Brennan STEP (VERIFIED); CB depth 1.5975 measured ; = OMi WebsitePartsInfo2026 row 530: overall length 2.89, hex 3.0, Side 1 / 2 ID 2.279 / 1.938 | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex / bores: review table = OMi WebsitePartsInfo2026 (identical values, checked 2026-10-09; first appended from the Brennan product drawing 2026-09-05 - OMi-only size: absent from Air-Way and MS51500G; OMi's data are Brennan's, evidence 2026-09-26 -&gt; one source, ASSUMED); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: two bores - the review-table counterbore CBDIA on its end, D3 through the rest - stepped at the HEX MID-PLANE (user 2026-10-09, Q-2404-BORE: the hole is not the same throughout (from OMi); ASSUMPTION for the step: no depth is published for this size - Air-Way prints none, MS51500G does not list it - Air-Way's 2404 / 2404-L drawings show the step inside the hex (2404-L at its middle), and the 14 two-bore 2404 parts measured 2026-10-01 have it at the hex mid-plane within 0.0005 - ASSUMED); -40 JIC END (2-1/2 in tube, 3-12 UN) IS NOT FROM MS33656J / THE 2403 TABLE: measured on the Brennan 2404-40-32 STEP (tip dia 2.400, 37deg seat 0.3185 to cone dia 2.880, land 0.0725, thread zone 0.7694 incl. the 45deg thread chamfer, 60deg ramp, relief 0.140 at the cone dia; end length 1.335) - single manufacturer, ASSUMED; MS33656J as printed differs (end length J 1.109, relief Q 0.125, tip D 2.380) - the Brennan geometry is used (project rule: geometry from Brennan STEPs); the extraction reproduces the 2403 -32 chain on the Brennan 2404-32-16 STEP; Brennan catalog 2408-40 L - hex width = 1.333 agrees</t>
+          <t>Brennan STEP measured == MS33656J published (VERIFIED) ; bores: OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 527 (= Air-Way D / D1 to rounding) (2026-10-09) | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: two bores - the review-table counterbore CBDIA on its end, D3 through the rest - stepped at the HEX MID-PLANE (user 2026-10-09, Q-2404-BORE: the hole is not the same throughout (from OMi); ASSUMPTION for the step: no depth is published for this size - Air-Way prints none, MS51500G does not list it - Air-Way's 2404 / 2404-L drawings show the step inside the hex (2404-L at its middle), and the 14 two-bore 2404 parts measured 2026-10-01 have it at the hex mid-plane within 0.0005 - ASSUMED)</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>2026-10-09: counterbore depth 1.5975 (Brennan STEP) replaced by the hex mid-plane rule (same position within 0.0002; no Brennan-only number, ruling 2026-10-08) | DataStatus VERIFIED -&gt; ASSUMED: every source of this OMi-only size is Brennan (product drawing, STEP; OMi's data are Brennan's) = one source; JICM radius 1.5000 is above the hex flats 1.5000 - the hex cut will flat it</t>
+          <t>2026-10-09 Q-2404-BORE (user, from OMi: the hole is not the same throughout): two bores, JIC 1.781 / pipe 1.5 from OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 527 (= Air-Way D / D1 to rounding); step at the hex mid-plane (Air-Way prints no depth, its drawing shows the step inside the hex)</t>
         </is>
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>2404-40-32</t>
+          <t>2404-32-24</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -8556,67 +8555,70 @@
         <is>
           <t>Trivalent Cr3 Zinc</t>
         </is>
+      </c>
+      <c r="AQ53" t="n">
+        <v>1500</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2404-L-04-04</t>
+          <t>2404-32-32</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2.25</v>
+        <v>3.11</v>
       </c>
       <c r="C54" t="n">
-        <v>0.32332</v>
+        <v>1.51554</v>
       </c>
       <c r="D54" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.625</v>
       </c>
       <c r="E54" t="n">
-        <v>0.26092</v>
+        <v>1.16929</v>
       </c>
       <c r="F54" t="n">
-        <v>0.4018</v>
+        <v>0.7565</v>
       </c>
       <c r="G54" t="n">
         <v>1.7899</v>
       </c>
       <c r="H54" t="n">
-        <v>0.1582</v>
+        <v>0.2735</v>
       </c>
       <c r="I54" t="n">
-        <v>0.52183</v>
+        <v>2.33859</v>
       </c>
       <c r="J54" t="n">
-        <v>0.4018</v>
+        <v>0.7565</v>
       </c>
       <c r="K54" t="n">
-        <v>0.05556</v>
+        <v>0.08696</v>
       </c>
       <c r="L54" t="n">
-        <v>0.26092</v>
+        <v>1.16929</v>
       </c>
       <c r="M54" t="n">
-        <v>0.21647</v>
+        <v>1.09973</v>
       </c>
       <c r="N54" t="n">
-        <v>0.21875</v>
+        <v>1.25</v>
       </c>
       <c r="O54" t="n">
-        <v>0.075</v>
+        <v>0.125</v>
       </c>
       <c r="P54" t="n">
-        <v>0.2608</v>
+        <v>0.7124</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.182</v>
+        <v>1.19</v>
       </c>
       <c r="R54" t="n">
-        <v>0.0795</v>
+        <v>0.1292</v>
       </c>
       <c r="S54" t="n">
-        <v>0.1135</v>
+        <v>0.3318</v>
       </c>
       <c r="T54" t="n">
         <v>60</v>
@@ -8625,43 +8627,43 @@
         <v>37</v>
       </c>
       <c r="V54" t="n">
-        <v>0.4375</v>
+        <v>2.5</v>
       </c>
       <c r="W54" t="n">
-        <v>0.05</v>
+        <v>0.08333</v>
       </c>
       <c r="X54" t="n">
-        <v>0.4538</v>
+        <v>1.1734</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.02706</v>
+        <v>0.04511</v>
       </c>
       <c r="Z54" t="n">
-        <v>0.0125</v>
+        <v>0.02083</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.05</v>
+        <v>0.08333</v>
       </c>
       <c r="AB54" t="n">
-        <v>0.28</v>
+        <v>1.938</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.13</v>
+        <v>1.37</v>
       </c>
       <c r="AD54" t="n">
-        <v>0.17</v>
+        <v>1.781</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.12</v>
+        <v>1.74</v>
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>2404-L-04-04</t>
+          <t>2404-32-32</t>
         </is>
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>Male Long Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 7/16-20 x 1/4-18</t>
+          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 2 1/2-12 x 2-11 1/2</t>
         </is>
       </c>
       <c r="AH54" t="inlineStr">
@@ -8671,94 +8673,102 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>1/4-18 NPTF</t>
+          <t>2-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>7/16-20</t>
+          <t>2 1/2-12</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AL54" t="inlineStr">
         <is>
-          <t>Air-Way s65 only (double-pass 8 rows); JIC end axials VERIFIED (MS33656J); long body length single-source | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; 2404-L = the LONG male connector (OMi "Straight-Long", Air-Way s65, DesignTable_2404L.xlsx), folded into the 2404 master (user decision 2026-09-25): overall = Air-Way L20, hex = C, bores D (JIC side) / D1 (pipe side); NPTF end length = the 2404 / 5404 value for the pipe dash; the hex takes the extra length: hex = L20 - both ends (= Air-Way T20 to within 0.007 on every row; Brennan 2404-L-08-08 STEP: JIC end 0.657, hex 1.633, pipe end 0.750, overall 3.040); bore: two bores - 2404-L table D1 from the pipe end, D from the JIC end - stepped at the HEX MID-PLANE (user 2026-10-09, Q-2404-BORE: the hole is not the same throughout; Air-Way publishes no depth for 2404-L and its series-65 drawing shows the step in the middle of the hex - ASSUMED)</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>bore: 2404-L table D 0.17 (JIC) / D1 0.28 (pipe), stepped at the hex mid-plane (user 2026-10-09, Q-2404-BORE); hex length 1.1400 (L20 - both ends) vs Air-Way T20 1.14: agree</t>
+          <t>Brennan STEP measured == MS33656J published (VERIFIED) | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: through passage = the smaller of D / D1, the end carrying the larger counterbored to depth S (MS51500G Note 5 and its S column; hand-made 2404 table CBCUT columns)</t>
         </is>
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>2404-L-04-04</t>
-        </is>
+          <t>2404-32-32</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Carbon Steel</t>
+        </is>
+      </c>
+      <c r="AP54" t="inlineStr">
+        <is>
+          <t>Trivalent Cr3 Zinc</t>
+        </is>
+      </c>
+      <c r="AQ54" t="n">
+        <v>1500</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2404-L-06-04</t>
+          <t>2404-40-32</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2.25</v>
+        <v>2.89</v>
       </c>
       <c r="C55" t="n">
-        <v>0.36373</v>
+        <v>1.73205</v>
       </c>
       <c r="D55" t="n">
-        <v>0.63</v>
+        <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>0.26092</v>
+        <v>1.16929</v>
       </c>
       <c r="F55" t="n">
-        <v>0.4018</v>
+        <v>0.7565</v>
       </c>
       <c r="G55" t="n">
         <v>1.7899</v>
       </c>
       <c r="H55" t="n">
-        <v>0.1582</v>
+        <v>0.2735</v>
       </c>
       <c r="I55" t="n">
-        <v>0.52183</v>
+        <v>2.33859</v>
       </c>
       <c r="J55" t="n">
-        <v>0.4018</v>
+        <v>0.7565</v>
       </c>
       <c r="K55" t="n">
-        <v>0.05556</v>
+        <v>0.08696</v>
       </c>
       <c r="L55" t="n">
-        <v>0.26092</v>
+        <v>1.16929</v>
       </c>
       <c r="M55" t="n">
-        <v>0.21647</v>
+        <v>1.09973</v>
       </c>
       <c r="N55" t="n">
-        <v>0.28125</v>
+        <v>1.5</v>
       </c>
       <c r="O55" t="n">
-        <v>0.083</v>
+        <v>0.14</v>
       </c>
       <c r="P55" t="n">
-        <v>0.2515</v>
+        <v>0.7694</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.2405</v>
+        <v>1.44</v>
       </c>
       <c r="R55" t="n">
-        <v>0.0898</v>
+        <v>0.0725</v>
       </c>
       <c r="S55" t="n">
-        <v>0.1082</v>
+        <v>0.3185</v>
       </c>
       <c r="T55" t="n">
         <v>60</v>
@@ -8767,43 +8777,43 @@
         <v>37</v>
       </c>
       <c r="V55" t="n">
-        <v>0.5625</v>
+        <v>3</v>
       </c>
       <c r="W55" t="n">
-        <v>0.05556</v>
+        <v>0.08333</v>
       </c>
       <c r="X55" t="n">
-        <v>0.4495</v>
+        <v>1.1604</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.03007</v>
+        <v>0.04511</v>
       </c>
       <c r="Z55" t="n">
-        <v>0.01389</v>
+        <v>0.02083</v>
       </c>
       <c r="AA55" t="n">
-        <v>0.05556</v>
+        <v>0.08333</v>
       </c>
       <c r="AB55" t="n">
-        <v>0.28</v>
+        <v>1.938</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.127</v>
+        <v>1.2925</v>
       </c>
       <c r="AD55" t="n">
-        <v>0.3</v>
+        <v>2.279</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.123</v>
+        <v>1.5975</v>
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>2404-L-06-04</t>
+          <t>2404-40-32</t>
         </is>
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>Male Long Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 9/16-18 x 1/4-18</t>
+          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 3-12 x 2-11 1/2</t>
         </is>
       </c>
       <c r="AH55" t="inlineStr">
@@ -8813,12 +8823,12 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>1/4-18 NPTF</t>
+          <t>2-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>9/16-18</t>
+          <t>3-12</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -8828,79 +8838,89 @@
       </c>
       <c r="AL55" t="inlineStr">
         <is>
-          <t>Air-Way s65 only (double-pass 8 rows); JIC end axials VERIFIED (MS33656J); long body length single-source | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; 2404-L = the LONG male connector (OMi "Straight-Long", Air-Way s65, DesignTable_2404L.xlsx), folded into the 2404 master (user decision 2026-09-25): overall = Air-Way L20, hex = C, bores D (JIC side) / D1 (pipe side); NPTF end length = the 2404 / 5404 value for the pipe dash; the hex takes the extra length: hex = L20 - both ends (= Air-Way T20 to within 0.007 on every row; Brennan 2404-L-08-08 STEP: JIC end 0.657, hex 1.633, pipe end 0.750, overall 3.040); bore: two bores - 2404-L table D1 from the pipe end, D from the JIC end - stepped at the HEX MID-PLANE (user 2026-10-09, Q-2404-BORE: the hole is not the same throughout; Air-Way publishes no depth for 2404-L and its series-65 drawing shows the step in the middle of the hex - ASSUMED)</t>
+          <t>Brennan product drawing 2026-09-05 (OMi-only SKU; absent from Air-Way) ; L matches Brennan STEP (VERIFIED); CB depth 1.5975 measured ; = OMi WebsitePartsInfo2026 row 530: overall length 2.89, hex 3.0, Side 1 / 2 ID 2.279 / 1.938 | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex / bores: review table = OMi WebsitePartsInfo2026 (identical values, checked 2026-10-09; first appended from the Brennan product drawing 2026-09-05 - OMi-only size: absent from Air-Way and MS51500G; OMi's data are Brennan's, evidence 2026-09-26 -&gt; one source, ASSUMED); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: two bores - the review-table counterbore CBDIA on its end, D3 through the rest - stepped at the HEX MID-PLANE (user 2026-10-09, Q-2404-BORE: the hole is not the same throughout (from OMi); ASSUMPTION for the step: no depth is published for this size - Air-Way prints none, MS51500G does not list it - Air-Way's 2404 / 2404-L drawings show the step inside the hex (2404-L at its middle), and the 14 two-bore 2404 parts measured 2026-10-01 have it at the hex mid-plane within 0.0005 - ASSUMED); -40 JIC END (2-1/2 in tube, 3-12 UN) IS NOT FROM MS33656J / THE 2403 TABLE: measured on the Brennan 2404-40-32 STEP (tip dia 2.400, 37deg seat 0.3185 to cone dia 2.880, land 0.0725, thread zone 0.7694 incl. the 45deg thread chamfer, 60deg ramp, relief 0.140 at the cone dia; end length 1.335) - single manufacturer, ASSUMED; MS33656J as printed differs (end length J 1.109, relief Q 0.125, tip D 2.380) - the Brennan geometry is used (project rule: geometry from Brennan STEPs); the extraction reproduces the 2403 -32 chain on the Brennan 2404-32-16 STEP; Brennan catalog 2408-40 L - hex width = 1.333 agrees</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>bore: 2404-L table D 0.3 (JIC) / D1 0.28 (pipe), stepped at the hex mid-plane (user 2026-10-09, Q-2404-BORE); hex length 1.1340 (L20 - both ends) vs Air-Way T20 1.13: agree</t>
+          <t>2026-10-09: counterbore depth 1.5975 (Brennan STEP) replaced by the hex mid-plane rule (same position within 0.0002; no Brennan-only number, ruling 2026-10-08) | DataStatus VERIFIED -&gt; ASSUMED: every source of this OMi-only size is Brennan (product drawing, STEP; OMi's data are Brennan's) = one source; JICM radius 1.5000 is above the hex flats 1.5000 - the hex cut will flat it</t>
         </is>
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>2404-L-06-04</t>
+          <t>2404-40-32</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Carbon Steel</t>
+        </is>
+      </c>
+      <c r="AP55" t="inlineStr">
+        <is>
+          <t>Trivalent Cr3 Zinc</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2404-L-06-06</t>
+          <t>2404-L-04-04</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="C56" t="n">
-        <v>0.43301</v>
+        <v>0.32332</v>
       </c>
       <c r="D56" t="n">
-        <v>0.75</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E56" t="n">
-        <v>0.32823</v>
+        <v>0.26092</v>
       </c>
       <c r="F56" t="n">
-        <v>0.4078</v>
+        <v>0.4018</v>
       </c>
       <c r="G56" t="n">
         <v>1.7899</v>
       </c>
       <c r="H56" t="n">
-        <v>0.1522</v>
+        <v>0.1582</v>
       </c>
       <c r="I56" t="n">
-        <v>0.65645</v>
+        <v>0.52183</v>
       </c>
       <c r="J56" t="n">
-        <v>0.4078</v>
+        <v>0.4018</v>
       </c>
       <c r="K56" t="n">
         <v>0.05556</v>
       </c>
       <c r="L56" t="n">
-        <v>0.32823</v>
+        <v>0.26092</v>
       </c>
       <c r="M56" t="n">
-        <v>0.28378</v>
+        <v>0.21647</v>
       </c>
       <c r="N56" t="n">
-        <v>0.28125</v>
+        <v>0.21875</v>
       </c>
       <c r="O56" t="n">
-        <v>0.083</v>
+        <v>0.075</v>
       </c>
       <c r="P56" t="n">
-        <v>0.2515</v>
+        <v>0.2608</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.2405</v>
+        <v>0.182</v>
       </c>
       <c r="R56" t="n">
-        <v>0.0898</v>
+        <v>0.0795</v>
       </c>
       <c r="S56" t="n">
-        <v>0.1082</v>
+        <v>0.1135</v>
       </c>
       <c r="T56" t="n">
         <v>60</v>
@@ -8909,43 +8929,43 @@
         <v>37</v>
       </c>
       <c r="V56" t="n">
-        <v>0.5625</v>
+        <v>0.4375</v>
       </c>
       <c r="W56" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="X56" t="n">
-        <v>0.4495</v>
+        <v>0.4538</v>
       </c>
       <c r="Y56" t="n">
-        <v>0.03007</v>
+        <v>0.02706</v>
       </c>
       <c r="Z56" t="n">
-        <v>0.01389</v>
+        <v>0.0125</v>
       </c>
       <c r="AA56" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="AB56" t="n">
-        <v>0.41</v>
+        <v>0.28</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.252</v>
+        <v>1.13</v>
       </c>
       <c r="AD56" t="n">
-        <v>0.3</v>
+        <v>0.17</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.248</v>
+        <v>1.12</v>
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>2404-L-06-06</t>
+          <t>2404-L-04-04</t>
         </is>
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>Male Long Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 9/16-18 x 3/8-18</t>
+          <t>Male Long Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 7/16-20 x 1/4-18</t>
         </is>
       </c>
       <c r="AH56" t="inlineStr">
@@ -8955,12 +8975,12 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>3/8-18 NPTF</t>
+          <t>1/4-18 NPTF</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>9/16-18</t>
+          <t>7/16-20</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -8975,74 +8995,74 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>bore: 2404-L table D 0.3 (JIC) / D1 0.41 (pipe), stepped at the hex mid-plane (user 2026-10-09, Q-2404-BORE); hex length 1.3840 (L20 - both ends) vs Air-Way T20 1.38: agree</t>
+          <t>bore: 2404-L table D 0.17 (JIC) / D1 0.28 (pipe), stepped at the hex mid-plane (user 2026-10-09, Q-2404-BORE); hex length 1.1400 (L20 - both ends) vs Air-Way T20 1.14: agree</t>
         </is>
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>2404-L-06-06</t>
+          <t>2404-L-04-04</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2404-L-08-08</t>
+          <t>2404-L-06-04</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3.03</v>
+        <v>2.25</v>
       </c>
       <c r="C57" t="n">
-        <v>0.50807</v>
+        <v>0.36373</v>
       </c>
       <c r="D57" t="n">
-        <v>0.88</v>
+        <v>0.63</v>
       </c>
       <c r="E57" t="n">
-        <v>0.40779</v>
+        <v>0.26092</v>
       </c>
       <c r="F57" t="n">
-        <v>0.5337</v>
+        <v>0.4018</v>
       </c>
       <c r="G57" t="n">
         <v>1.7899</v>
       </c>
       <c r="H57" t="n">
-        <v>0.2163</v>
+        <v>0.1582</v>
       </c>
       <c r="I57" t="n">
-        <v>0.81557</v>
+        <v>0.52183</v>
       </c>
       <c r="J57" t="n">
-        <v>0.5337</v>
+        <v>0.4018</v>
       </c>
       <c r="K57" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="L57" t="n">
-        <v>0.40779</v>
+        <v>0.26092</v>
       </c>
       <c r="M57" t="n">
-        <v>0.35064</v>
+        <v>0.21647</v>
       </c>
       <c r="N57" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="O57" t="n">
-        <v>0.094</v>
+        <v>0.083</v>
       </c>
       <c r="P57" t="n">
-        <v>0.2837</v>
+        <v>0.2515</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.3295</v>
+        <v>0.2405</v>
       </c>
       <c r="R57" t="n">
-        <v>0.0984</v>
+        <v>0.0898</v>
       </c>
       <c r="S57" t="n">
-        <v>0.1546</v>
+        <v>0.1082</v>
       </c>
       <c r="T57" t="n">
         <v>60</v>
@@ -9051,43 +9071,43 @@
         <v>37</v>
       </c>
       <c r="V57" t="n">
-        <v>0.75</v>
+        <v>0.5625</v>
       </c>
       <c r="W57" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="X57" t="n">
-        <v>0.5367</v>
+        <v>0.4495</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.03383</v>
+        <v>0.03007</v>
       </c>
       <c r="Z57" t="n">
-        <v>0.01562</v>
+        <v>0.01389</v>
       </c>
       <c r="AA57" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="AB57" t="n">
-        <v>0.53</v>
+        <v>0.28</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.5615</v>
+        <v>1.127</v>
       </c>
       <c r="AD57" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.4685</v>
+        <v>1.123</v>
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>2404-L-08-08</t>
+          <t>2404-L-06-04</t>
         </is>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>Male Long Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 3/4-16 x 1/2-14</t>
+          <t>Male Long Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 9/16-18 x 1/4-18</t>
         </is>
       </c>
       <c r="AH57" t="inlineStr">
@@ -9097,12 +9117,12 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF</t>
+          <t>1/4-18 NPTF</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>3/4-16</t>
+          <t>9/16-18</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -9117,74 +9137,74 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>bore: 2404-L table D 0.39 (JIC) / D1 0.53 (pipe), stepped at the hex mid-plane (user 2026-10-09, Q-2404-BORE); hex length 1.6230 (L20 - both ends) vs Air-Way T20 1.63: differ by -0.0070 (L20 printed to 2 decimals)</t>
+          <t>bore: 2404-L table D 0.3 (JIC) / D1 0.28 (pipe), stepped at the hex mid-plane (user 2026-10-09, Q-2404-BORE); hex length 1.1340 (L20 - both ends) vs Air-Way T20 1.13: agree</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>2404-L-08-08</t>
+          <t>2404-L-06-04</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2404-L-12-12</t>
+          <t>2404-L-06-06</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="C58" t="n">
-        <v>0.65241</v>
+        <v>0.43301</v>
       </c>
       <c r="D58" t="n">
-        <v>1.13</v>
+        <v>0.75</v>
       </c>
       <c r="E58" t="n">
-        <v>0.51241</v>
+        <v>0.32823</v>
       </c>
       <c r="F58" t="n">
-        <v>0.5457</v>
+        <v>0.4078</v>
       </c>
       <c r="G58" t="n">
         <v>1.7899</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2043</v>
+        <v>0.1522</v>
       </c>
       <c r="I58" t="n">
-        <v>1.02482</v>
+        <v>0.65645</v>
       </c>
       <c r="J58" t="n">
-        <v>0.5457</v>
+        <v>0.4078</v>
       </c>
       <c r="K58" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="L58" t="n">
-        <v>0.51241</v>
+        <v>0.32823</v>
       </c>
       <c r="M58" t="n">
-        <v>0.45527</v>
+        <v>0.28378</v>
       </c>
       <c r="N58" t="n">
-        <v>0.53125</v>
+        <v>0.28125</v>
       </c>
       <c r="O58" t="n">
-        <v>0.125</v>
+        <v>0.083</v>
       </c>
       <c r="P58" t="n">
-        <v>0.3895</v>
+        <v>0.2515</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.4715</v>
+        <v>0.2405</v>
       </c>
       <c r="R58" t="n">
-        <v>0.1299</v>
+        <v>0.0898</v>
       </c>
       <c r="S58" t="n">
-        <v>0.1851</v>
+        <v>0.1082</v>
       </c>
       <c r="T58" t="n">
         <v>60</v>
@@ -9193,76 +9213,360 @@
         <v>37</v>
       </c>
       <c r="V58" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="W58" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="X58" t="n">
+        <v>0.4495</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>0.03007</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>0.01389</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1.252</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>1.248</v>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>2404-L-06-06</t>
+        </is>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>Male Long Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 9/16-18 x 3/8-18</t>
+        </is>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>2404</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>3/8-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>9/16-18</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AL58" t="inlineStr">
+        <is>
+          <t>Air-Way s65 only (double-pass 8 rows); JIC end axials VERIFIED (MS33656J); long body length single-source | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; 2404-L = the LONG male connector (OMi "Straight-Long", Air-Way s65, DesignTable_2404L.xlsx), folded into the 2404 master (user decision 2026-09-25): overall = Air-Way L20, hex = C, bores D (JIC side) / D1 (pipe side); NPTF end length = the 2404 / 5404 value for the pipe dash; the hex takes the extra length: hex = L20 - both ends (= Air-Way T20 to within 0.007 on every row; Brennan 2404-L-08-08 STEP: JIC end 0.657, hex 1.633, pipe end 0.750, overall 3.040); bore: two bores - 2404-L table D1 from the pipe end, D from the JIC end - stepped at the HEX MID-PLANE (user 2026-10-09, Q-2404-BORE: the hole is not the same throughout; Air-Way publishes no depth for 2404-L and its series-65 drawing shows the step in the middle of the hex - ASSUMED)</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>bore: 2404-L table D 0.3 (JIC) / D1 0.41 (pipe), stepped at the hex mid-plane (user 2026-10-09, Q-2404-BORE); hex length 1.3840 (L20 - both ends) vs Air-Way T20 1.38: agree</t>
+        </is>
+      </c>
+      <c r="AN58" t="inlineStr">
+        <is>
+          <t>2404-L-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2404-L-08-08</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.50807</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="G59" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.2163</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.81557</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0.2837</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0.0984</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0.1546</v>
+      </c>
+      <c r="T59" t="n">
+        <v>60</v>
+      </c>
+      <c r="U59" t="n">
+        <v>37</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="W59" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="X59" t="n">
+        <v>0.5367</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>1.5615</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>1.4685</v>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>2404-L-08-08</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>Male Long Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 3/4-16 x 1/2-14</t>
+        </is>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>2404</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>1/2-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>3/4-16</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AL59" t="inlineStr">
+        <is>
+          <t>Air-Way s65 only (double-pass 8 rows); JIC end axials VERIFIED (MS33656J); long body length single-source | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; 2404-L = the LONG male connector (OMi "Straight-Long", Air-Way s65, DesignTable_2404L.xlsx), folded into the 2404 master (user decision 2026-09-25): overall = Air-Way L20, hex = C, bores D (JIC side) / D1 (pipe side); NPTF end length = the 2404 / 5404 value for the pipe dash; the hex takes the extra length: hex = L20 - both ends (= Air-Way T20 to within 0.007 on every row; Brennan 2404-L-08-08 STEP: JIC end 0.657, hex 1.633, pipe end 0.750, overall 3.040); bore: two bores - 2404-L table D1 from the pipe end, D from the JIC end - stepped at the HEX MID-PLANE (user 2026-10-09, Q-2404-BORE: the hole is not the same throughout; Air-Way publishes no depth for 2404-L and its series-65 drawing shows the step in the middle of the hex - ASSUMED)</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>bore: 2404-L table D 0.39 (JIC) / D1 0.53 (pipe), stepped at the hex mid-plane (user 2026-10-09, Q-2404-BORE); hex length 1.6230 (L20 - both ends) vs Air-Way T20 1.63: differ by -0.0070 (L20 printed to 2 decimals)</t>
+        </is>
+      </c>
+      <c r="AN59" t="inlineStr">
+        <is>
+          <t>2404-L-08-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2404-L-12-12</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.65241</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.51241</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.5457</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.2043</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1.02482</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.5457</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.51241</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.45527</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0.4715</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0.1299</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0.1851</v>
+      </c>
+      <c r="T60" t="n">
+        <v>60</v>
+      </c>
+      <c r="U60" t="n">
+        <v>37</v>
+      </c>
+      <c r="V60" t="n">
         <v>1.0625</v>
       </c>
-      <c r="W58" t="n">
+      <c r="W60" t="n">
         <v>0.08333</v>
       </c>
-      <c r="X58" t="n">
+      <c r="X60" t="n">
         <v>0.7045</v>
       </c>
-      <c r="Y58" t="n">
+      <c r="Y60" t="n">
         <v>0.04511</v>
       </c>
-      <c r="Z58" t="n">
+      <c r="Z60" t="n">
         <v>0.02083</v>
       </c>
-      <c r="AA58" t="n">
+      <c r="AA60" t="n">
         <v>0.08333</v>
       </c>
-      <c r="AB58" t="n">
+      <c r="AB60" t="n">
         <v>0.72</v>
       </c>
-      <c r="AC58" t="n">
+      <c r="AC60" t="n">
         <v>1.693</v>
       </c>
-      <c r="AD58" t="n">
+      <c r="AD60" t="n">
         <v>0.61</v>
       </c>
-      <c r="AE58" t="n">
+      <c r="AE60" t="n">
         <v>1.807</v>
       </c>
-      <c r="AF58" t="inlineStr">
+      <c r="AF60" t="inlineStr">
         <is>
           <t>2404-L-12-12</t>
         </is>
       </c>
-      <c r="AG58" t="inlineStr">
+      <c r="AG60" t="inlineStr">
         <is>
           <t>Male Long Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 1 1/16-12 x 3/4-14</t>
         </is>
       </c>
-      <c r="AH58" t="inlineStr">
+      <c r="AH60" t="inlineStr">
         <is>
           <t>2404</t>
         </is>
       </c>
-      <c r="AI58" t="inlineStr">
+      <c r="AI60" t="inlineStr">
         <is>
           <t>3/4-14 NPTF</t>
         </is>
       </c>
-      <c r="AJ58" t="inlineStr">
+      <c r="AJ60" t="inlineStr">
         <is>
           <t>1 1/16-12</t>
         </is>
       </c>
-      <c r="AK58" t="inlineStr">
+      <c r="AK60" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="AL58" t="inlineStr">
+      <c r="AL60" t="inlineStr">
         <is>
           <t>Air-Way s65 only (double-pass 8 rows); JIC end axials VERIFIED (MS33656J); long body length single-source | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; 2404-L = the LONG male connector (OMi "Straight-Long", Air-Way s65, DesignTable_2404L.xlsx), folded into the 2404 master (user decision 2026-09-25): overall = Air-Way L20, hex = C, bores D (JIC side) / D1 (pipe side); NPTF end length = the 2404 / 5404 value for the pipe dash; the hex takes the extra length: hex = L20 - both ends (= Air-Way T20 to within 0.007 on every row; Brennan 2404-L-08-08 STEP: JIC end 0.657, hex 1.633, pipe end 0.750, overall 3.040); bore: two bores - 2404-L table D1 from the pipe end, D from the JIC end - stepped at the HEX MID-PLANE (user 2026-10-09, Q-2404-BORE: the hole is not the same throughout; Air-Way publishes no depth for 2404-L and its series-65 drawing shows the step in the middle of the hex - ASSUMED)</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
+      <c r="AM60" t="inlineStr">
         <is>
           <t>bore: 2404-L table D 0.61 (JIC) / D1 0.72 (pipe), stepped at the hex mid-plane (user 2026-10-09, Q-2404-BORE); hex length 1.8860 (L20 - both ends) vs Air-Way T20 1.89: agree</t>
         </is>
       </c>
-      <c r="AN58" t="inlineStr">
+      <c r="AN60" t="inlineStr">
         <is>
           <t>2404-L-12-12</t>
         </is>

--- a/04_DESIGN_TABLES/DesignTable_2404_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2404_SW2.xlsx
@@ -4124,7 +4124,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="C25" t="n">
         <v>0.54271</v>
@@ -4205,13 +4205,13 @@
         <v>0.281</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="AD25" t="n">
         <v>0.484</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.944</v>
+        <v>0.949</v>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
@@ -4245,12 +4245,12 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>Brennan STEP measured == MS33656J published (VERIFIED) ; bores: OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 498 (= Air-Way D / D1 to rounding) (2026-10-09) | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: two bores - the review-table counterbore CBDIA on its end, D3 through the rest - stepped at the HEX MID-PLANE (user 2026-10-09, Q-2404-BORE: the hole is not the same throughout (from OMi); ASSUMPTION for the step: no depth is published for this size - Air-Way prints none, MS51500G does not list it - Air-Way's 2404 / 2404-L drawings show the step inside the hex (2404-L at its middle), and the 14 two-bore 2404 parts measured 2026-10-01 have it at the hex mid-plane within 0.0005 - ASSUMED)</t>
+          <t>Brennan STEP measured == MS33656J published (VERIFIED) ; bores: OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 498 (= Air-Way D / D1 to rounding) (2026-10-09); D1@DRIVE: Air-Way 1.7 (raw 07_RAW_EXTRACTS (2404.csv col 5 L); OMi file / Brennan 1.69) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: two bores - the review-table counterbore CBDIA on its end, D3 through the rest - stepped at the HEX MID-PLANE (user 2026-10-09, Q-2404-BORE: the hole is not the same throughout (from OMi); ASSUMPTION for the step: no depth is published for this size - Air-Way prints none, MS51500G does not list it - Air-Way's 2404 / 2404-L drawings show the step inside the hex (2404-L at its middle), and the 14 two-bore 2404 parts measured 2026-10-01 have it at the hex mid-plane within 0.0005 - ASSUMED)</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>2026-10-09: overall length 1.69 from OMi (row 498; was 1.7, question 26 / OMi first) ; 2026-10-09 Q-2404-BORE (user, from OMi: the hole is not the same throughout): two bores, JIC 0.484 / pipe 0.281 from OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 498 (= Air-Way D / D1 to rounding); step at the hex mid-plane (Air-Way prints no depth, its drawing shows the step inside the hex)</t>
+          <t>2026-10-09: overall length 1.69 from OMi (row 498; was 1.7, question 26 / OMi first) ; 2026-10-09 Q-2404-BORE (user, from OMi: the hole is not the same throughout): two bores, JIC 0.484 / pipe 0.281 from OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 498 (= Air-Way D / D1 to rounding); step at the hex mid-plane (Air-Way prints no depth, its drawing shows the step inside the hex) | 2026-10-20 Air-Way first: D1@DRIVE OMi/Brennan 1.69 -&gt; Air-Way 1.7</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
@@ -7490,7 +7490,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="C47" t="n">
         <v>1.44338</v>
@@ -7571,13 +7571,13 @@
         <v>1.937</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.406</v>
+        <v>1.401</v>
       </c>
       <c r="AD47" t="n">
         <v>1.078</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.334</v>
+        <v>1.329</v>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
@@ -7611,12 +7611,12 @@
       </c>
       <c r="AL47" t="inlineStr">
         <is>
-          <t>Brennan STEP measured == MS33656J published (VERIFIED) ; bores: OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 520 (= Air-Way D / D1 to rounding) (2026-10-09) | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: two bores - the review-table counterbore CBDIA on its end, D3 through the rest - stepped at the HEX MID-PLANE (user 2026-10-09, Q-2404-BORE: the hole is not the same throughout (from OMi); ASSUMPTION for the step: no depth is published for this size - Air-Way prints none, MS51500G does not list it - Air-Way's 2404 / 2404-L drawings show the step inside the hex (2404-L at its middle), and the 14 two-bore 2404 parts measured 2026-10-01 have it at the hex mid-plane within 0.0005 - ASSUMED)</t>
+          <t>Brennan STEP measured == MS33656J published (VERIFIED) ; bores: OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 520 (= Air-Way D / D1 to rounding) (2026-10-09); D1@DRIVE: Air-Way 2.73 (raw 07_RAW_EXTRACTS (2404.csv col 5 L); OMi file / Brennan 2.74) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; bore: two bores - the review-table counterbore CBDIA on its end, D3 through the rest - stepped at the HEX MID-PLANE (user 2026-10-09, Q-2404-BORE: the hole is not the same throughout (from OMi); ASSUMPTION for the step: no depth is published for this size - Air-Way prints none, MS51500G does not list it - Air-Way's 2404 / 2404-L drawings show the step inside the hex (2404-L at its middle), and the 14 two-bore 2404 parts measured 2026-10-01 have it at the hex mid-plane within 0.0005 - ASSUMED)</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>2026-10-09: overall length 2.74 from OMi (row 520; was 2.73, question 26 / OMi first) ; 2026-10-09 Q-2404-BORE (user, from OMi: the hole is not the same throughout): two bores, JIC 1.078 / pipe 1.937 from OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 520 (= Air-Way D / D1 to rounding); step at the hex mid-plane (Air-Way prints no depth, its drawing shows the step inside the hex)</t>
+          <t>2026-10-09: overall length 2.74 from OMi (row 520; was 2.73, question 26 / OMi first) ; 2026-10-09 Q-2404-BORE (user, from OMi: the hole is not the same throughout): two bores, JIC 1.078 / pipe 1.937 from OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 520 (= Air-Way D / D1 to rounding); step at the hex mid-plane (Air-Way prints no depth, its drawing shows the step inside the hex) | 2026-10-20 Air-Way first: D1@DRIVE OMi/Brennan 2.74 -&gt; Air-Way 2.73</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_2404_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2404_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ60"/>
+  <dimension ref="A1:AQ61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9569,6 +9569,148 @@
       <c r="AN60" t="inlineStr">
         <is>
           <t>2404-L-12-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2404-L-32-32</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1.51554</v>
+      </c>
+      <c r="D61" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="G61" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.2735</v>
+      </c>
+      <c r="I61" t="n">
+        <v>2.33859</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="L61" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1.09973</v>
+      </c>
+      <c r="N61" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0.7124</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="T61" t="n">
+        <v>60</v>
+      </c>
+      <c r="U61" t="n">
+        <v>37</v>
+      </c>
+      <c r="V61" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W61" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="X61" t="n">
+        <v>1.1734</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>1.938</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>2.6585</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>1.781</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>2.9615</v>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>2404-L-32-32</t>
+        </is>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>Male Long Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 2 1/2-12 x 2-11 1/2</t>
+        </is>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>2404</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>2 1/2-12</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AL61" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-21] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-21 (batch 19 C, staged): Brennan allowed (user 2026-10-18 "yes use brennan but still differentiate"); Air-Way prints no value for this part number, OMi's website file gives no dimension; sizes from the Brennan TFA catalog, each checked on the part's OWN Brennan STEP (09_STEP_FILES/BRENNAN_2404-L-32-32.stp, every value equal to the catalog within 0.005); end details from the end library: L20@DRIVE: Brennan TFA catalog p.6 table TFA-p006-t03 "2404-L MJ-MP STRAIGHT LONG" row 2404-L-32-32 col "L LGTH" = "5.620" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 529.3, page verified True) [Brennan = yes 2026-10-18] - overall length; own STEP: overall 5.6204 (bbox -1.3332 .. 4.2872, C_ownstep/measure/2404-L-32-32.txt + 2404-L-32-32_axial_section.txt (nptfm40.py, jicm.py, axial section)); CHEX@HEX: Brennan TFA catalog p.6 table TFA-p006-t03 "2404-L MJ-MP STRAIGHT LONG" row 2404-L-32-32 col "C HEX" = "2.625" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 529.3, page verified True) [Brennan = yes 2026-10-18] - body hex; own STEP: hex corner radius 1.5158 = A/F 2.6254, hex 0 .. 3.257 (C_ownstep/measure/2404-L-32-32.txt + 2404-L-32-32_axial_section.txt (nptfm40.py, jicm.py, axial section)); D@BORE: Brennan TFA catalog p.6 table TFA-p006-t03 "2404-L MJ-MP STRAIGHT LONG" row 2404-L-32-32 col "B1 DRILL" = "1.781" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 529.3, page verified True) [Brennan = yes 2026-10-18] - JIC-end bore; own STEP: bore 1.781 from the JIC tip to 1.6285 = the hex mid-plane (C_ownstep/measure/2404-L-32-32.txt + 2404-L-32-32_axial_section.txt (nptfm40.py, jicm.py, axial section)); D1@BORE: Brennan TFA catalog p.6 table TFA-p006-t03 "2404-L MJ-MP STRAIGHT LONG" row 2404-L-32-32 col "A2 DRILL" = "1.938" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 529.3, page verified True) [Brennan = yes 2026-10-18] - pipe-end bore; own STEP: bore 1.938 from the hex mid-plane to the pipe tip (C_ownstep/measure/2404-L-32-32.txt + 2404-L-32-32_axial_section.txt (nptfm40.py, jicm.py, axial section)) - confirms the "likely" pairing of wave 2 and the generator rule "two bores stepped at the hex mid-plane" (Q-2404-BORE 2026-10-09); THDMAJ_B@DRIVE: end library: male JIC -32 thread major = 2.5 (gen_straight2 JIC[32] = MS33656J chain of templates/DesignTable_2403_SW2.xlsx, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] (own STEP: JIC end 1.333 = the -32 chain: TM 2.5, SL 0.3318, CD 2.38, LL 0.1292, TZ 0.7124, RL 0.125); THDMAJ_A@DRIVE: end library: pipe OD of the -32 NPTF thread = 2.375 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[32]) [Q-TRANSFER-ENDLIB yes 2026-10-08] (own STEP: collar 2.375, male NPTF end 1.03 = ENDL[32]) | MODEL: male NPTF end (End A) per ASME B1.20.3 (tip major E0+0.8P, cone over L2 at 1.7899 deg, then a plain relief to the end length) with the end length NPTF_ENDL of the 2404 table (= the 5404 Brennan-measured value of the pipe dash); this REPLACES the hand-built pipe end (plain cylinder of pipe OD, taper left to the SolidWorks pipe-thread feature) by the library NPTF end of 5404 / 6401 / 2706; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan; -40: JIC_MEAS_40 measured on the Brennan 2404-40-32 STEP, equal to the -40 chain of the hand-made 2404 table row); overall length D1 / hex: review table (Air-Way; == MS51500G on the sizes it lists); hex over the whole length between the two ends; hex end chamfers NOT modelled; 2404-L = the LONG male connector (OMi "Straight-Long", Air-Way s65, DesignTable_2404L.xlsx), folded into the 2404 master (user decision 2026-09-25): overall = Air-Way L20, hex = C, bores D (JIC side) / D1 (pipe side); NPTF end length = the 2404 / 5404 value for the pipe dash; the hex takes the extra length: hex = L20 - both ends (= Air-Way T20 to within 0.007 on every row; Brennan 2404-L-08-08 STEP: JIC end 0.657, hex 1.633, pipe end 0.750, overall 3.040); bore: two bores - 2404-L table D1 from the pipe end, D from the JIC end - stepped at the HEX MID-PLANE (user 2026-10-09, Q-2404-BORE: the hole is not the same throughout; Air-Way publishes no depth for 2404-L and its series-65 drawing shows the step in the middle of the hex - ASSUMED)</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-21 batch 19 C (staged, not shipped): filled from the Brennan TFA catalog, checked on the own STEP (tools/_out/batch19_20261021/C_ownstep/measure); marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate). Cross-check only: Air-Way prints no -32 2404-L row | bore: 2404-L table D 1.781 (JIC) / D1 1.938 (pipe), stepped at the hex mid-plane (user 2026-10-09, Q-2404-BORE)</t>
+        </is>
+      </c>
+      <c r="AN61" t="inlineStr">
+        <is>
+          <t>2404-L-32-32</t>
         </is>
       </c>
     </row>
